--- a/java22 database design/Java22 PNhung Database Design.xlsx
+++ b/java22 database design/Java22 PNhung Database Design.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Studying\Java22\3.DATABASE\java22 database patches\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Studying\Java22\3.DATABASE\java22 database design\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9165" tabRatio="724" firstSheet="4" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
     <sheet name="B2. Mô hình logic" sheetId="2" r:id="rId2"/>
     <sheet name="B3. Mô hình vật lý" sheetId="4" r:id="rId3"/>
     <sheet name="B3. Xử lý mối quan hệ" sheetId="6" r:id="rId4"/>
-    <sheet name="Bn. Tạo dữ liệu kiểm thử(mẫu)" sheetId="5" r:id="rId5"/>
+    <sheet name="B3. Mô hình vật lý WIP" sheetId="7" r:id="rId5"/>
+    <sheet name="B4.Tạo dữ liệu kiểm thử" sheetId="8" r:id="rId6"/>
+    <sheet name="Bn. Tạo dữ liệu kiểm thử(mẫu)" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -45,7 +47,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -62,7 +64,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -79,7 +81,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -96,7 +98,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -113,7 +115,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -130,7 +132,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -147,7 +149,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -745,7 +747,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -761,6 +763,215 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>tc={85B16A7D-4DA7-409D-A477-42471121604E}</author>
+    <author>tc={FEB531F8-3F37-41C2-9572-96E04C8ECAC8}</author>
+    <author>tc={9DB5297B-73D2-42AE-9A76-79B839CE1D77}</author>
+    <author>tc={4B47AF2D-C770-4A5E-8158-147A119469B1}</author>
+  </authors>
+  <commentList>
+    <comment ref="M6" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Chờ xử lý
+Đã được xử lý chờ đóng gói
+Đang đóng gói
+Đang giao hàng
+Giao hàng thành công
+Giao hàng thất bại
+Hủy đơn hàng
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="1" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    1 MH chỉ có 1 Giá Mua
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="2" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Lưu lịch sử mua hàng của từng khách hàng</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N22" authorId="3" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Có rất nhiều màu sắc color, rgb, hexa -&gt; sử dụng varchar để lưu chứ k tạo 1 bảng riêng</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>tc={FEB531F8-3F37-41C2-9572-96E04C8ECAC8}</author>
+    <author>tc={598B10B6-E6F1-40B5-B6AD-C3AD129CB648}</author>
+    <author>tc={9DB5297B-73D2-42AE-9A76-79B839CE1D77}</author>
+    <author>tc={F417F53F-78F4-4FB2-9932-6B06E3741ADD}</author>
+    <author>tc={89D0F75C-16FA-43DB-9BE0-099B1CAFC699}</author>
+    <author>tc={81011C5D-5AE3-44B3-97CD-014DF419A278}</author>
+  </authors>
+  <commentList>
+    <comment ref="G47" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    1 MH chỉ có 1 Giá Mua
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C79" authorId="1" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Thanh toán khi nhận hàng
+Thanh toán online - chuyển khoản
+Thanh toán online - thẻ ghi nợ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H100" authorId="2" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Lưu lịch sử mua hàng của từng khách hàng</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C183" authorId="3" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Chờ xác nhận, Đang đóng gói, Đóng gói hoàn thành chờ vận chuyển, Đang vận chuyển, Giao hàng thành công, Giao hàng thất bại, Hủy đơn hàng</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B193" authorId="4" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Không cần thuộc phòng ban, làm được mọi chức năng</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I194" authorId="5" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    NhanVien, Quan Ly</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={3503BA87-F97B-4BA2-B285-74026B5E7BB4}</author>
@@ -781,7 +992,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -798,7 +1009,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -815,7 +1026,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -832,7 +1043,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -849,7 +1060,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -917,7 +1128,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -935,7 +1146,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -977,7 +1188,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -994,7 +1205,7 @@
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Arial"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
@@ -1010,7 +1221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="498">
   <si>
     <r>
       <t xml:space="preserve">Xác định các </t>
@@ -1020,7 +1231,7 @@
         <b/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1030,7 +1241,7 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -2122,23 +2333,442 @@
   <si>
     <t>C02_ITEM_GROUP_ID</t>
   </si>
+  <si>
+    <t>ChiTietDonHang</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>PK(DonHang,MatHang)</t>
+  </si>
+  <si>
+    <t>QUAN HE N-N: TẠO BẢNG MỚI</t>
+  </si>
+  <si>
+    <t>MaHD</t>
+  </si>
+  <si>
+    <t>TenDH</t>
+  </si>
+  <si>
+    <t>có thể bỏ khóa ngoại ở bảng bất kì</t>
+  </si>
+  <si>
+    <t>nhưng phải dựa logic từng bài toán</t>
+  </si>
+  <si>
+    <t>QUAN HE 1-1</t>
+  </si>
+  <si>
+    <t>unique(DonHang,MatHang)</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>cách 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cách 2 : dùng nhiều hơn </t>
+  </si>
+  <si>
+    <t>T100_SUPPLIER</t>
+  </si>
+  <si>
+    <t>T101_SUPPLIER_CHAIN</t>
+  </si>
+  <si>
+    <t>T03_ITEM_DETAIL</t>
+  </si>
+  <si>
+    <t>T04_ORDER</t>
+  </si>
+  <si>
+    <t>T05_ORDER_DETAIL</t>
+  </si>
+  <si>
+    <t>T06_ORDER_STATUS_DETAIL</t>
+  </si>
+  <si>
+    <t>T07_BILL</t>
+  </si>
+  <si>
+    <t>T08_CUSTOMER</t>
+  </si>
+  <si>
+    <t>T09_PAYMENT_METHOD</t>
+  </si>
+  <si>
+    <t>T10_ORDER_STATUS</t>
+  </si>
+  <si>
+    <t>T11_TITLE</t>
+  </si>
+  <si>
+    <t>T12_SIZE</t>
+  </si>
+  <si>
+    <t>T13_EMPLOYEE</t>
+  </si>
+  <si>
+    <t>C101_SID</t>
+  </si>
+  <si>
+    <t>C03_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C04_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C07_BILL_ID</t>
+  </si>
+  <si>
+    <t>C08_CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>C09_PM_ID</t>
+  </si>
+  <si>
+    <t>C10_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C11_TITLE_ID</t>
+  </si>
+  <si>
+    <t>C13_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C101_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C03_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C04_RECEIVER_NAME</t>
+  </si>
+  <si>
+    <t>C05_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C06_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C07_DELIVERY_FEE</t>
+  </si>
+  <si>
+    <t>C08_CUSTOMER_NAME</t>
+  </si>
+  <si>
+    <t>C09_PM_TYPE</t>
+  </si>
+  <si>
+    <t>C10_STATUS_DESC</t>
+  </si>
+  <si>
+    <t>C11_TITLE_NAME</t>
+  </si>
+  <si>
+    <t>C12_SIZE_NAME</t>
+  </si>
+  <si>
+    <t>C13_EMPLOYEE_NAME</t>
+  </si>
+  <si>
+    <t>C101_SUPPLIER_ID</t>
+  </si>
+  <si>
+    <t>C03_SIZE_ID</t>
+  </si>
+  <si>
+    <t>C04_RECEIVER_PHONE</t>
+  </si>
+  <si>
+    <t>C05_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C06_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C07_TOTAL_OF_MONEY</t>
+  </si>
+  <si>
+    <t>C08_CUSTOMER_EMAIL</t>
+  </si>
+  <si>
+    <t>C12_GENDER</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>C101_AMOUNT</t>
+  </si>
+  <si>
+    <t>C03_COLOR</t>
+  </si>
+  <si>
+    <t>C04_DELIVERY_ADDRESS</t>
+  </si>
+  <si>
+    <t>C05_AMOUNT</t>
+  </si>
+  <si>
+    <t>C06_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C07_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C08_CUSTOMER_PHONE</t>
+  </si>
+  <si>
+    <t>C12_DESC</t>
+  </si>
+  <si>
+    <t>C101_ENTERING_DATE</t>
+  </si>
+  <si>
+    <t>C03_AMOUNT</t>
+  </si>
+  <si>
+    <t>C08_CUSTOMER_ADDRESS</t>
+  </si>
+  <si>
+    <t>C03_SALES_PRICE</t>
+  </si>
+  <si>
+    <t>C04_ORDER_TIME</t>
+  </si>
+  <si>
+    <t>C08_CUSTOMER_PASSWORD</t>
+  </si>
+  <si>
+    <t>C04_CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>C13_TITLE_ID</t>
+  </si>
+  <si>
+    <t>C100_SUPPLIER_ID</t>
+  </si>
+  <si>
+    <t>C100_SUPPLIER_NAME</t>
+  </si>
+  <si>
+    <t>C100_SUPPLIER_TAX</t>
+  </si>
+  <si>
+    <t>NCC_S1</t>
+  </si>
+  <si>
+    <t>NCC_S2</t>
+  </si>
+  <si>
+    <t>NCC_S3</t>
+  </si>
+  <si>
+    <t>NCC_S4</t>
+  </si>
+  <si>
+    <t>NCC_S5</t>
+  </si>
+  <si>
+    <t>AUTO_INCREMENT</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t>[220, 400, 582, 600, 300]</t>
+  </si>
+  <si>
+    <t>Là ngày/ giờ hiện tại</t>
+  </si>
+  <si>
+    <t>-2 ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mặt Hàng 1-4</t>
+  </si>
+  <si>
+    <t>Mặt Hàng 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mặt Hàng 5-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mặt Hàng 9-12</t>
+  </si>
+  <si>
+    <t>Mặt Hàng bé hơn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mặt Hàng 12-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mặt Hàng 16-20</t>
+  </si>
+  <si>
+    <t>[100, 120, 140, 160, 180, 200]</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>100 records</t>
+  </si>
+  <si>
+    <t>Unique(item, supplier, date)</t>
+  </si>
+  <si>
+    <t>Thanh toán khi nhận hàng</t>
+  </si>
+  <si>
+    <t>Thanh toán online - chuyển khoản</t>
+  </si>
+  <si>
+    <t>Thanh toán online - ghi nợ</t>
+  </si>
+  <si>
+    <t>Khách Hàng 1</t>
+  </si>
+  <si>
+    <t>Khách Hàng 2</t>
+  </si>
+  <si>
+    <t>Khách Hàng 3</t>
+  </si>
+  <si>
+    <t>Khách Hàng 4</t>
+  </si>
+  <si>
+    <t>Khách Hàng 5</t>
+  </si>
+  <si>
+    <t>Khách Hàng 6</t>
+  </si>
+  <si>
+    <t>Khách Hàng 7</t>
+  </si>
+  <si>
+    <t>Khách Hàng 8</t>
+  </si>
+  <si>
+    <t>Khách Hàng 9</t>
+  </si>
+  <si>
+    <t>Khách Hàng 10</t>
+  </si>
+  <si>
+    <t>AUTO_INCREMENT[1-20]</t>
+  </si>
+  <si>
+    <t>Người nhận X[id]</t>
+  </si>
+  <si>
+    <t>Địa chỉ X[id]</t>
+  </si>
+  <si>
+    <t>C04_PAYMENT_METHOD_ID</t>
+  </si>
+  <si>
+    <t>Random ID của PAYMENT_METHOD</t>
+  </si>
+  <si>
+    <t>SYSDATE - 1h - loop</t>
+  </si>
+  <si>
+    <t>Đon Hàng 2,12 của KH 2</t>
+  </si>
+  <si>
+    <t>Đon Hàng 1,11 của KH 1</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>Khi bảng N-N-N… thì có khóa chính là 1 colum mới làm khóa chính</t>
+  </si>
+  <si>
+    <t>--&gt; Khi truy vấn dữ liệu chỉ cần truy vấn cho khóa chính theo 1 colum</t>
+  </si>
+  <si>
+    <t>--&gt; Nếu đây là bảng cha , bảng con liên kết đến, trong bảng con chỉ cần tạo 1 colum</t>
+  </si>
+  <si>
+    <t>C06_OS_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C06_LAST_UPDATE</t>
+  </si>
+  <si>
+    <t>Xử lí khi làm bài tập</t>
+  </si>
+  <si>
+    <t>C10_ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C10_ORDER_STATUS_DESC</t>
+  </si>
+  <si>
+    <t>C13_EMPLOYEE_EMAIL</t>
+  </si>
+  <si>
+    <t>C13_EMPLOYEE_ADDRESS</t>
+  </si>
+  <si>
+    <t>C13_EMPLOYEE_PHONE</t>
+  </si>
+  <si>
+    <t>C13_EMPLOYEE_USERNAME</t>
+  </si>
+  <si>
+    <t>C13_EMPLOYEE_PASSWORD</t>
+  </si>
+  <si>
+    <t>red, yellow, blue, green, orange</t>
+  </si>
+  <si>
+    <t>Sử dụng dữ liệu từ các bảng ITEM, SIZE
+---
+ITEM, SIZE có ID lẻ: AMOUNT = 185, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5
+ITEM, SIZE có ID chẵn: AMOUNT = 220, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5 + 20
+---
+1 ITEM có thể có nhiều BUY_PRICE, lấy max BUY_PRICE trong 6 tháng gần nhất</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2146,7 +2776,7 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2154,7 +2784,7 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFFC000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2162,14 +2792,14 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2177,7 +2807,7 @@
       <u/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2185,14 +2815,14 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF00B050"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFC00000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2200,13 +2830,13 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFC00000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2214,14 +2844,14 @@
       <u/>
       <sz val="12"/>
       <color rgb="FF00B050"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF7030A0"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2229,7 +2859,7 @@
       <strike/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2250,26 +2880,26 @@
       <u/>
       <sz val="12"/>
       <color rgb="FF7030A0"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2277,7 +2907,7 @@
       <u/>
       <sz val="12"/>
       <color theme="8" tint="0.39997558519241921"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2299,7 +2929,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2319,12 +2949,34 @@
     <font>
       <sz val="12"/>
       <color theme="8" tint="0.39997558519241921"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2373,8 +3025,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -2542,11 +3200,161 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2699,27 +3507,12 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2754,15 +3547,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2791,6 +3575,190 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3171,36 +4139,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:L35"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.4375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="14.6875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.6875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.46484375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1328125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="14.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="20" style="1" customWidth="1"/>
-    <col min="12" max="29" width="14.6875" style="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.125" style="1"/>
+    <col min="12" max="29" width="14.6640625" style="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="39" t="s">
         <v>280</v>
       </c>
@@ -3227,7 +4195,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="40" t="s">
         <v>287</v>
       </c>
@@ -3254,7 +4222,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="40" t="s">
         <v>294</v>
       </c>
@@ -3281,7 +4249,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="40" t="s">
         <v>301</v>
       </c>
@@ -3304,7 +4272,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="40" t="s">
         <v>304</v>
       </c>
@@ -3323,7 +4291,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="40" t="s">
         <v>306</v>
       </c>
@@ -3342,7 +4310,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="40" t="s">
         <v>309</v>
       </c>
@@ -3361,7 +4329,7 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="40" t="s">
         <v>311</v>
       </c>
@@ -3378,7 +4346,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="40" t="s">
         <v>313</v>
       </c>
@@ -3394,7 +4362,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="40" t="s">
         <v>297</v>
       </c>
@@ -3411,7 +4379,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="40" t="s">
         <v>281</v>
       </c>
@@ -3428,7 +4396,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="40"/>
       <c r="C15" s="46"/>
       <c r="D15" s="45" t="s">
@@ -3443,7 +4411,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="40"/>
       <c r="C16" s="40"/>
       <c r="D16" s="40"/>
@@ -3456,7 +4424,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -3469,7 +4437,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -3482,29 +4450,29 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="20" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="21" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="23" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="24" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D24" s="5"/>
     </row>
-    <row r="25" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="26" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="27" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="28" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="29" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="30" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="31" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="32" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="33" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="34" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="35" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3514,27 +4482,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:O32"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.0625" style="38" customWidth="1"/>
-    <col min="6" max="6" width="19.125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="14.6875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.06640625" style="38" customWidth="1"/>
+    <col min="6" max="6" width="19.1328125" style="1" customWidth="1"/>
+    <col min="7" max="8" width="14.6640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="20" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="27" width="14.6875" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.125" style="1"/>
+    <col min="10" max="10" width="18.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="27" width="14.6640625" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>117</v>
       </c>
@@ -3542,7 +4510,7 @@
       <c r="D2" s="5"/>
       <c r="E2" s="43"/>
     </row>
-    <row r="3" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -3553,7 +4521,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:15" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="39" t="s">
         <v>280</v>
       </c>
@@ -3589,7 +4557,7 @@
       <c r="N4" s="38"/>
       <c r="O4" s="38"/>
     </row>
-    <row r="5" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="47" t="s">
         <v>287</v>
       </c>
@@ -3599,7 +4567,7 @@
       <c r="D5" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="55" t="s">
         <v>289</v>
       </c>
       <c r="F5" s="51" t="s">
@@ -3625,14 +4593,14 @@
       <c r="N5" s="38"/>
       <c r="O5" s="38"/>
     </row>
-    <row r="6" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="40" t="s">
         <v>294</v>
       </c>
       <c r="C6" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="56" t="s">
         <v>328</v>
       </c>
       <c r="E6" s="49" t="s">
@@ -3661,7 +4629,7 @@
       <c r="N6" s="38"/>
       <c r="O6" s="38"/>
     </row>
-    <row r="7" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="40" t="s">
         <v>301</v>
       </c>
@@ -3689,7 +4657,7 @@
       <c r="N7" s="38"/>
       <c r="O7" s="38"/>
     </row>
-    <row r="8" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="40" t="s">
         <v>304</v>
       </c>
@@ -3715,7 +4683,7 @@
       <c r="N8" s="38"/>
       <c r="O8" s="38"/>
     </row>
-    <row r="9" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="48" t="s">
         <v>281</v>
       </c>
@@ -3737,7 +4705,7 @@
       <c r="N9" s="38"/>
       <c r="O9" s="38"/>
     </row>
-    <row r="10" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="40" t="s">
         <v>311</v>
       </c>
@@ -3759,7 +4727,7 @@
       <c r="N10" s="38"/>
       <c r="O10" s="38"/>
     </row>
-    <row r="11" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="48" t="s">
         <v>313</v>
       </c>
@@ -3779,7 +4747,7 @@
       <c r="N11" s="38"/>
       <c r="O11" s="38"/>
     </row>
-    <row r="12" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="40" t="s">
         <v>297</v>
       </c>
@@ -3798,7 +4766,7 @@
       <c r="N12" s="38"/>
       <c r="O12" s="38"/>
     </row>
-    <row r="13" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="40" t="s">
         <v>319</v>
       </c>
@@ -3818,7 +4786,7 @@
       <c r="N13" s="38"/>
       <c r="O13" s="38"/>
     </row>
-    <row r="14" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="40"/>
       <c r="C14" s="46"/>
       <c r="D14" s="48" t="s">
@@ -3836,13 +4804,13 @@
       <c r="N14" s="38"/>
       <c r="O14" s="38"/>
     </row>
-    <row r="15" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L15" s="38"/>
       <c r="M15" s="38"/>
       <c r="N15" s="38"/>
       <c r="O15" s="38"/>
     </row>
-    <row r="16" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="1" t="s">
         <v>2</v>
       </c>
@@ -3850,7 +4818,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="1" t="s">
         <v>3</v>
       </c>
@@ -3859,33 +4827,33 @@
       </c>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="1" t="s">
         <v>5</v>
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="1" t="s">
         <v>13</v>
       </c>
@@ -3893,7 +4861,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="1" t="s">
         <v>14</v>
       </c>
@@ -3901,38 +4869,38 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="26" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="1" t="s">
         <v>332</v>
       </c>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="1" t="s">
         <v>333</v>
       </c>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="1" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B32" s="1" t="s">
         <v>335</v>
       </c>
@@ -3947,34 +4915,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:P64"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="54.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="33.3125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.5625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.5625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="54.59765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.1328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.53125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.53125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.53125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.86328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.1328125" style="1" customWidth="1"/>
     <col min="11" max="11" width="27" style="1" customWidth="1"/>
-    <col min="12" max="12" width="30.5625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="22.6875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22.3125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="28.6875" style="1" customWidth="1"/>
-    <col min="17" max="29" width="14.6875" style="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.125" style="1"/>
+    <col min="12" max="12" width="30.53125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.1328125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="22.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="28.6640625" style="1" customWidth="1"/>
+    <col min="17" max="29" width="14.6640625" style="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>118</v>
       </c>
@@ -3983,7 +4951,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -3998,7 +4966,7 @@
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="2:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:16" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="39" t="s">
         <v>336</v>
       </c>
@@ -4035,35 +5003,35 @@
       <c r="O4" s="23"/>
       <c r="P4" s="14"/>
     </row>
-    <row r="5" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="62" t="s">
+    <row r="5" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="57" t="s">
         <v>359</v>
       </c>
-      <c r="D5" s="62" t="s">
+      <c r="D5" s="57" t="s">
         <v>289</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="58" t="s">
         <v>289</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="59" t="s">
         <v>291</v>
       </c>
-      <c r="G5" s="62" t="s">
+      <c r="G5" s="57" t="s">
         <v>292</v>
       </c>
-      <c r="H5" s="62" t="s">
+      <c r="H5" s="57" t="s">
         <v>293</v>
       </c>
-      <c r="I5" s="62" t="s">
+      <c r="I5" s="57" t="s">
         <v>321</v>
       </c>
-      <c r="J5" s="62" t="s">
+      <c r="J5" s="57" t="s">
         <v>323</v>
       </c>
-      <c r="K5" s="62" t="s">
+      <c r="K5" s="57" t="s">
         <v>324</v>
       </c>
       <c r="L5" s="7"/>
@@ -4072,14 +5040,14 @@
       <c r="O5" s="13"/>
       <c r="P5" s="13"/>
     </row>
-    <row r="6" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="40" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="56" t="s">
         <v>328</v>
       </c>
       <c r="E6" s="49" t="s">
@@ -4109,7 +5077,7 @@
       <c r="O6" s="27"/>
       <c r="P6" s="13"/>
     </row>
-    <row r="7" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="40" t="s">
         <v>301</v>
       </c>
@@ -4138,7 +5106,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="4"/>
     </row>
-    <row r="8" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="40" t="s">
         <v>47</v>
       </c>
@@ -4165,7 +5133,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="48" t="s">
         <v>67</v>
       </c>
@@ -4188,7 +5156,7 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="40" t="s">
         <v>311</v>
       </c>
@@ -4211,7 +5179,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="48" t="s">
         <v>313</v>
       </c>
@@ -4232,7 +5200,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="40" t="s">
         <v>297</v>
       </c>
@@ -4253,7 +5221,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="40" t="s">
         <v>319</v>
       </c>
@@ -4274,7 +5242,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="40"/>
       <c r="C14" s="46"/>
       <c r="D14" s="48" t="s">
@@ -4293,7 +5261,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="40"/>
       <c r="C15" s="46"/>
       <c r="D15" s="40"/>
@@ -4310,7 +5278,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="40"/>
       <c r="C16" s="40"/>
       <c r="D16" s="40"/>
@@ -4327,7 +5295,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4344,7 +5312,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4361,25 +5329,25 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="20" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="9" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="25"/>
     </row>
-    <row r="21" spans="2:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="52" t="s">
+    <row r="21" spans="2:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-    </row>
-    <row r="22" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="126"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="128"/>
+    </row>
+    <row r="22" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="9" t="s">
         <v>20</v>
       </c>
@@ -4388,34 +5356,34 @@
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
     </row>
-    <row r="23" spans="2:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="52" t="s">
+    <row r="23" spans="2:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="127"/>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
     </row>
-    <row r="24" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="9" t="s">
         <v>23</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="2:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="52" t="s">
+    <row r="25" spans="2:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
+      <c r="C25" s="129"/>
+      <c r="D25" s="129"/>
+      <c r="E25" s="129"/>
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="9" t="s">
         <v>25</v>
       </c>
@@ -4425,48 +5393,48 @@
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
     </row>
-    <row r="27" spans="2:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="52" t="s">
+    <row r="27" spans="2:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="126"/>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="2:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="52" t="s">
+    <row r="28" spans="2:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="126" t="s">
         <v>337</v>
       </c>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
+      <c r="C28" s="127"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="127"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="2:16" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="52" t="s">
+    <row r="29" spans="2:16" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B29" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
+      <c r="C29" s="127"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="127"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="10" t="s">
         <v>28</v>
       </c>
@@ -4474,7 +5442,7 @@
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="1" t="s">
         <v>29</v>
       </c>
@@ -4482,7 +5450,7 @@
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
     </row>
-    <row r="34" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="12" t="s">
         <v>30</v>
       </c>
@@ -4492,7 +5460,7 @@
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
     </row>
-    <row r="35" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B35" s="1" t="s">
         <v>31</v>
       </c>
@@ -4500,30 +5468,30 @@
       <c r="G35" s="22"/>
       <c r="H35" s="5"/>
     </row>
-    <row r="36" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G36" s="8"/>
     </row>
-    <row r="37" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B37" s="1" t="s">
         <v>32</v>
       </c>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B38" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B39" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B41" s="9" t="s">
         <v>33</v>
       </c>
@@ -4532,24 +5500,24 @@
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B42" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B43" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B44" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="46" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="47" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B47" s="1" t="s">
         <v>42</v>
       </c>
@@ -4557,7 +5525,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B48" s="1" t="s">
         <v>44</v>
       </c>
@@ -4565,9 +5533,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="51" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="50" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="51" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="11" t="s">
         <v>91</v>
       </c>
@@ -4576,7 +5544,7 @@
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
     </row>
-    <row r="52" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B52" s="24" t="s">
         <v>92</v>
       </c>
@@ -4585,21 +5553,21 @@
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
     </row>
-    <row r="53" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
     </row>
-    <row r="54" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
     </row>
-    <row r="55" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B55" s="11" t="s">
         <v>93</v>
       </c>
@@ -4608,7 +5576,7 @@
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
     </row>
-    <row r="56" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B56" s="24" t="s">
         <v>94</v>
       </c>
@@ -4617,14 +5585,14 @@
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
     </row>
-    <row r="57" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="58" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="59" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="60" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="63" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="64" spans="2:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B29:E29"/>
@@ -4642,566 +5610,4560 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I34"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:AE47"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="16.3125" customWidth="1"/>
-    <col min="4" max="4" width="8.25" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.265625" customWidth="1"/>
+    <col min="5" max="5" width="20.59765625" customWidth="1"/>
     <col min="7" max="7" width="9" style="37"/>
-    <col min="8" max="8" width="8.4375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.625" customWidth="1"/>
+    <col min="8" max="8" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.59765625" customWidth="1"/>
+    <col min="13" max="13" width="13.3984375" customWidth="1"/>
+    <col min="15" max="15" width="7.796875" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" customWidth="1"/>
+    <col min="20" max="20" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-    </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B2" s="71" t="s">
+    <row r="1" spans="2:31" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+    </row>
+    <row r="2" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B2" s="136" t="s">
         <v>351</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="73"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B3" s="74" t="s">
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="138"/>
+      <c r="K2" s="136" t="s">
+        <v>368</v>
+      </c>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
+      <c r="U2" s="138"/>
+      <c r="W2" s="136" t="s">
+        <v>373</v>
+      </c>
+      <c r="X2" s="137"/>
+      <c r="Y2" s="137"/>
+      <c r="Z2" s="137"/>
+      <c r="AA2" s="137"/>
+      <c r="AB2" s="137"/>
+      <c r="AC2" s="137"/>
+      <c r="AD2" s="137"/>
+      <c r="AE2" s="138"/>
+    </row>
+    <row r="3" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B3" s="66" t="s">
         <v>348</v>
       </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70" t="s">
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65" t="s">
         <v>349</v>
       </c>
-      <c r="I3" s="75"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B4" s="74"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70" t="s">
+      <c r="I3" s="67"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="67"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="67"/>
+    </row>
+    <row r="4" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B4" s="66"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65" t="s">
         <v>356</v>
       </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="75"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B5" s="76" t="s">
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="67"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="67"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="67"/>
+    </row>
+    <row r="5" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B5" s="68" t="s">
         <v>280</v>
       </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="66" t="s">
+      <c r="C5" s="64"/>
+      <c r="D5" s="61" t="s">
         <v>350</v>
       </c>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="67" t="s">
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="I5" s="77"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B6" s="78" t="s">
+      <c r="I5" s="69"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="68" t="s">
+        <v>280</v>
+      </c>
+      <c r="M5" s="64"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="77" t="s">
+        <v>282</v>
+      </c>
+      <c r="T5" s="69"/>
+      <c r="U5" s="67"/>
+      <c r="W5" s="66"/>
+      <c r="X5" s="77" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y5" s="69"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="77" t="s">
+        <v>327</v>
+      </c>
+      <c r="AC5" s="61"/>
+      <c r="AD5" s="93"/>
+      <c r="AE5" s="67"/>
+    </row>
+    <row r="6" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B6" s="70" t="s">
         <v>287</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="63" t="s">
         <v>294</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="63" t="s">
         <v>281</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="68" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="63" t="s">
         <v>288</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="71" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B7" s="80">
+      <c r="K6" s="66"/>
+      <c r="L6" s="70" t="s">
+        <v>287</v>
+      </c>
+      <c r="M6" s="63" t="s">
+        <v>294</v>
+      </c>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="63" t="s">
+        <v>289</v>
+      </c>
+      <c r="T6" s="71" t="s">
+        <v>370</v>
+      </c>
+      <c r="U6" s="67"/>
+      <c r="W6" s="66"/>
+      <c r="X6" s="63" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y6" s="71" t="s">
+        <v>370</v>
+      </c>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="63" t="s">
+        <v>369</v>
+      </c>
+      <c r="AC6" s="63" t="s">
+        <v>316</v>
+      </c>
+      <c r="AD6" s="86" t="s">
+        <v>289</v>
+      </c>
+      <c r="AE6" s="67"/>
+    </row>
+    <row r="7" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B7" s="72">
         <v>1</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="61" t="s">
         <v>338</v>
       </c>
-      <c r="D7" s="66">
+      <c r="D7" s="61">
         <v>1</v>
       </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="66">
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="61">
         <v>1</v>
       </c>
-      <c r="I7" s="77" t="s">
+      <c r="I7" s="69" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B8" s="80">
+      <c r="K7" s="66"/>
+      <c r="L7" s="72" t="s">
+        <v>361</v>
+      </c>
+      <c r="M7" s="61" t="s">
+        <v>338</v>
+      </c>
+      <c r="N7" s="65"/>
+      <c r="O7" s="65"/>
+      <c r="P7" s="65"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="61">
+        <v>1</v>
+      </c>
+      <c r="T7" s="69" t="s">
+        <v>344</v>
+      </c>
+      <c r="U7" s="67"/>
+      <c r="W7" s="66"/>
+      <c r="X7" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="69" t="s">
+        <v>344</v>
+      </c>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="61">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="61" t="s">
+        <v>344</v>
+      </c>
+      <c r="AD7" s="94">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="67"/>
+    </row>
+    <row r="8" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B8" s="72">
         <v>2</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="61" t="s">
         <v>339</v>
       </c>
-      <c r="D8" s="66">
+      <c r="D8" s="61">
         <v>1</v>
       </c>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="66">
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="61">
         <v>2</v>
       </c>
-      <c r="I8" s="77" t="s">
+      <c r="I8" s="69" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B9" s="80">
+      <c r="K8" s="66"/>
+      <c r="L8" s="72" t="s">
+        <v>362</v>
+      </c>
+      <c r="M8" s="61" t="s">
+        <v>339</v>
+      </c>
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="61">
+        <v>2</v>
+      </c>
+      <c r="T8" s="69" t="s">
+        <v>345</v>
+      </c>
+      <c r="U8" s="67"/>
+      <c r="W8" s="66"/>
+      <c r="X8" s="61">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="69" t="s">
+        <v>345</v>
+      </c>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="61">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="61" t="s">
+        <v>345</v>
+      </c>
+      <c r="AD8" s="94">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="67"/>
+    </row>
+    <row r="9" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B9" s="72">
         <v>3</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="61" t="s">
         <v>340</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="61">
         <v>2</v>
       </c>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="66">
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="61">
         <v>3</v>
       </c>
-      <c r="I9" s="77" t="s">
+      <c r="I9" s="69" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B10" s="80">
+      <c r="K9" s="66"/>
+      <c r="L9" s="72" t="s">
+        <v>363</v>
+      </c>
+      <c r="M9" s="61" t="s">
+        <v>340</v>
+      </c>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
+      <c r="P9" s="65"/>
+      <c r="Q9" s="65"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="61">
+        <v>3</v>
+      </c>
+      <c r="T9" s="69" t="s">
+        <v>346</v>
+      </c>
+      <c r="U9" s="67"/>
+      <c r="W9" s="66"/>
+      <c r="X9" s="61">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="69" t="s">
+        <v>346</v>
+      </c>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="65"/>
+      <c r="AB9" s="61">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="61" t="s">
+        <v>346</v>
+      </c>
+      <c r="AD9" s="94">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="67"/>
+    </row>
+    <row r="10" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B10" s="72">
         <v>4</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="61" t="s">
         <v>341</v>
       </c>
-      <c r="D10" s="66">
+      <c r="D10" s="61">
         <v>3</v>
       </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="66">
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="61">
         <v>4</v>
       </c>
-      <c r="I10" s="77" t="s">
+      <c r="I10" s="69" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B11" s="80">
+      <c r="K10" s="66"/>
+      <c r="L10" s="72" t="s">
+        <v>364</v>
+      </c>
+      <c r="M10" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="N10" s="65"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="65"/>
+      <c r="Q10" s="65"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="61">
+        <v>4</v>
+      </c>
+      <c r="T10" s="69" t="s">
+        <v>347</v>
+      </c>
+      <c r="U10" s="67"/>
+      <c r="W10" s="66"/>
+      <c r="X10" s="61">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="69" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z10" s="65"/>
+      <c r="AA10" s="65"/>
+      <c r="AB10" s="61">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="61" t="s">
+        <v>347</v>
+      </c>
+      <c r="AD10" s="95">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="67"/>
+    </row>
+    <row r="11" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B11" s="72">
         <v>5</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C11" s="61" t="s">
         <v>342</v>
       </c>
-      <c r="D11" s="66">
+      <c r="D11" s="61">
         <v>3</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="75"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B12" s="80">
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="67"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="72" t="s">
+        <v>365</v>
+      </c>
+      <c r="M11" s="61" t="s">
+        <v>342</v>
+      </c>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="65"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="65"/>
+      <c r="S11" s="65"/>
+      <c r="T11" s="65"/>
+      <c r="U11" s="67"/>
+      <c r="W11" s="66"/>
+      <c r="X11" s="65"/>
+      <c r="Y11" s="65"/>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="65"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="65"/>
+      <c r="AD11" s="65"/>
+      <c r="AE11" s="67"/>
+    </row>
+    <row r="12" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="B12" s="72">
         <v>6</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="61" t="s">
         <v>343</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="61">
         <v>4</v>
       </c>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="75"/>
-    </row>
-    <row r="13" spans="2:9" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="81"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="87" t="s">
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="67"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="72" t="s">
+        <v>366</v>
+      </c>
+      <c r="M12" s="61" t="s">
+        <v>343</v>
+      </c>
+      <c r="N12" s="65"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="65" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q12" s="65"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="65"/>
+      <c r="U12" s="67"/>
+      <c r="W12" s="66"/>
+      <c r="X12" s="65"/>
+      <c r="Y12" s="65"/>
+      <c r="Z12" s="65" t="s">
+        <v>371</v>
+      </c>
+      <c r="AA12" s="65"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="65"/>
+      <c r="AD12" s="65"/>
+      <c r="AE12" s="67"/>
+    </row>
+    <row r="13" spans="2:31" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="79" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B14" s="71" t="s">
+      <c r="K13" s="66"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="67"/>
+      <c r="W13" s="66"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65" t="s">
+        <v>372</v>
+      </c>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="65"/>
+      <c r="AE13" s="67"/>
+    </row>
+    <row r="14" spans="2:31" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B14" s="136" t="s">
         <v>351</v>
       </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="73"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="74" t="s">
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="137"/>
+      <c r="G14" s="137"/>
+      <c r="H14" s="137"/>
+      <c r="I14" s="138"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="133" t="s">
+        <v>360</v>
+      </c>
+      <c r="P14" s="134"/>
+      <c r="Q14" s="135"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="67"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="65"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="65"/>
+      <c r="AD14" s="65"/>
+      <c r="AE14" s="67"/>
+    </row>
+    <row r="15" spans="2:31" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B15" s="66" t="s">
         <v>348</v>
       </c>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70" t="s">
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65" t="s">
         <v>349</v>
       </c>
-      <c r="I15" s="75"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="74"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="75"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B17" s="76" t="s">
+      <c r="I15" s="67"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="87" t="s">
+        <v>287</v>
+      </c>
+      <c r="P15" s="88" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q15" s="91" t="s">
+        <v>297</v>
+      </c>
+      <c r="R15" s="65"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="65"/>
+      <c r="U15" s="67"/>
+      <c r="W15" s="66"/>
+      <c r="X15" s="65"/>
+      <c r="Y15" s="65"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="65"/>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="65"/>
+      <c r="AD15" s="65"/>
+      <c r="AE15" s="67"/>
+    </row>
+    <row r="16" spans="2:31" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B16" s="66"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="67"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="89">
+        <v>1</v>
+      </c>
+      <c r="P16" s="90" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q16" s="92">
+        <v>2</v>
+      </c>
+      <c r="R16" s="65"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="65"/>
+      <c r="U16" s="67"/>
+      <c r="W16" s="73"/>
+      <c r="X16" s="74"/>
+      <c r="Y16" s="74"/>
+      <c r="Z16" s="74"/>
+      <c r="AA16" s="74"/>
+      <c r="AB16" s="74"/>
+      <c r="AC16" s="74"/>
+      <c r="AD16" s="74"/>
+      <c r="AE16" s="75"/>
+    </row>
+    <row r="17" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B17" s="68" t="s">
         <v>280</v>
       </c>
-      <c r="C17" s="69"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="67" t="s">
+      <c r="C17" s="64"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="I17" s="77"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="78" t="s">
+      <c r="I17" s="69"/>
+      <c r="K17" s="66"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="89">
+        <v>2</v>
+      </c>
+      <c r="P17" s="90" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q17" s="92">
+        <v>3</v>
+      </c>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="65"/>
+      <c r="U17" s="67"/>
+    </row>
+    <row r="18" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B18" s="70" t="s">
         <v>287</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="63" t="s">
         <v>294</v>
       </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="68" t="s">
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="63" t="s">
         <v>288</v>
       </c>
-      <c r="I18" s="79" t="s">
+      <c r="I18" s="71" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B19" s="80">
+      <c r="K18" s="66"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="89">
         <v>1</v>
       </c>
-      <c r="C19" s="66" t="s">
+      <c r="P18" s="90" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q18" s="92">
+        <v>2</v>
+      </c>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="65"/>
+      <c r="U18" s="67"/>
+    </row>
+    <row r="19" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B19" s="72">
+        <v>1</v>
+      </c>
+      <c r="C19" s="61" t="s">
         <v>338</v>
       </c>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="66">
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="61">
         <v>1</v>
       </c>
-      <c r="I19" s="77" t="s">
+      <c r="I19" s="69" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B20" s="80">
+      <c r="K19" s="66"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="89">
+        <v>1</v>
+      </c>
+      <c r="P19" s="90" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q19" s="92">
         <v>2</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="65"/>
+      <c r="U19" s="67"/>
+    </row>
+    <row r="20" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B20" s="72">
+        <v>2</v>
+      </c>
+      <c r="C20" s="61" t="s">
         <v>339</v>
       </c>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="66">
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="61">
         <v>2</v>
       </c>
-      <c r="I20" s="77" t="s">
+      <c r="I20" s="69" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B21" s="80">
+      <c r="K20" s="66"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="89">
+        <v>2</v>
+      </c>
+      <c r="P20" s="90" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q20" s="92">
+        <v>1</v>
+      </c>
+      <c r="R20" s="65"/>
+      <c r="S20" s="65"/>
+      <c r="T20" s="65"/>
+      <c r="U20" s="67"/>
+    </row>
+    <row r="21" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B21" s="72">
         <v>3</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="61" t="s">
         <v>340</v>
       </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="66">
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="61">
         <v>3</v>
       </c>
-      <c r="I21" s="77" t="s">
+      <c r="I21" s="69" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B22" s="80">
+      <c r="K21" s="66"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="89">
+        <v>3</v>
+      </c>
+      <c r="P21" s="90" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q21" s="92">
+        <v>1</v>
+      </c>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="65"/>
+      <c r="U21" s="67"/>
+    </row>
+    <row r="22" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="72">
         <v>4</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="61" t="s">
         <v>341</v>
       </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="66">
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="61">
         <v>4</v>
       </c>
-      <c r="I22" s="77" t="s">
+      <c r="I22" s="69" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B23" s="80">
+      <c r="K22" s="66"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="89">
+        <v>3</v>
+      </c>
+      <c r="P22" s="90" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q22" s="92">
+        <v>1</v>
+      </c>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="67"/>
+    </row>
+    <row r="23" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B23" s="72">
         <v>5</v>
       </c>
-      <c r="C23" s="66" t="s">
+      <c r="C23" s="61" t="s">
         <v>342</v>
       </c>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="75"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B24" s="80">
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="67"/>
+      <c r="K23" s="66"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="89">
+        <v>4</v>
+      </c>
+      <c r="P23" s="90" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q23" s="92">
+        <v>1</v>
+      </c>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="67"/>
+    </row>
+    <row r="24" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B24" s="72">
         <v>6</v>
       </c>
-      <c r="C24" s="66" t="s">
+      <c r="C24" s="61" t="s">
         <v>343</v>
       </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="75"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B25" s="74"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="85" t="s">
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="67"/>
+      <c r="K24" s="66"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="89">
+        <v>4</v>
+      </c>
+      <c r="P24" s="90" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q24" s="92">
+        <v>2</v>
+      </c>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
+      <c r="T24" s="65"/>
+      <c r="U24" s="67"/>
+    </row>
+    <row r="25" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B25" s="66"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="130" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="85"/>
-      <c r="G25" s="84"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="75"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B26" s="74"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="86" t="s">
+      <c r="F25" s="130"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="67"/>
+      <c r="K25" s="66"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="89">
+        <v>4</v>
+      </c>
+      <c r="P25" s="90" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q25" s="92">
+        <v>2</v>
+      </c>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
+      <c r="U25" s="67"/>
+    </row>
+    <row r="26" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B26" s="66"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="78" t="s">
         <v>353</v>
       </c>
-      <c r="F26" s="86"/>
-      <c r="G26" s="84"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="75"/>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B27" s="74"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="68" t="s">
+      <c r="F26" s="78"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="67"/>
+      <c r="K26" s="66"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="89">
+        <v>1</v>
+      </c>
+      <c r="P26" s="90" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q26" s="92">
+        <v>3</v>
+      </c>
+      <c r="R26" s="65"/>
+      <c r="S26" s="65"/>
+      <c r="T26" s="65"/>
+      <c r="U26" s="67"/>
+    </row>
+    <row r="27" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B27" s="66"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="63" t="s">
         <v>287</v>
       </c>
-      <c r="F27" s="68" t="s">
+      <c r="F27" s="63" t="s">
         <v>281</v>
       </c>
-      <c r="G27" s="84"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="75"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B28" s="74"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="66">
+      <c r="G27" s="76"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="67"/>
+      <c r="K27" s="66"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="89">
+        <v>2</v>
+      </c>
+      <c r="P27" s="90" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q27" s="92">
+        <v>2</v>
+      </c>
+      <c r="R27" s="65" t="s">
+        <v>376</v>
+      </c>
+      <c r="S27" s="65"/>
+      <c r="T27" s="65"/>
+      <c r="U27" s="67"/>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="B28" s="66"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="61">
         <v>1</v>
       </c>
-      <c r="F28" s="66">
+      <c r="F28" s="61">
         <v>1</v>
       </c>
-      <c r="G28" s="84"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="75"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B29" s="74"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="66">
+      <c r="G28" s="76"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="67"/>
+      <c r="K28" s="66" t="s">
+        <v>483</v>
+      </c>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="65"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="65"/>
+      <c r="S28" s="65"/>
+      <c r="T28" s="65"/>
+      <c r="U28" s="67"/>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="B29" s="66"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="61">
         <v>2</v>
       </c>
-      <c r="F29" s="66">
+      <c r="F29" s="61">
         <v>1</v>
       </c>
-      <c r="G29" s="84"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="75"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B30" s="74"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="66">
+      <c r="G29" s="76"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="67"/>
+      <c r="K29" s="125" t="s">
+        <v>484</v>
+      </c>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="65"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="65"/>
+      <c r="S29" s="65"/>
+      <c r="T29" s="65"/>
+      <c r="U29" s="67"/>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="B30" s="66"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="61">
         <v>3</v>
       </c>
-      <c r="F30" s="66">
+      <c r="F30" s="61">
         <v>2</v>
       </c>
-      <c r="G30" s="84"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="75"/>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B31" s="74"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="66">
+      <c r="G30" s="76"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="67"/>
+      <c r="K30" s="125" t="s">
+        <v>485</v>
+      </c>
+      <c r="L30" s="65"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="65"/>
+      <c r="P30" s="65"/>
+      <c r="Q30" s="65"/>
+      <c r="S30" s="65"/>
+      <c r="T30" s="65"/>
+      <c r="U30" s="67"/>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="B31" s="66"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="61">
         <v>4</v>
       </c>
-      <c r="F31" s="66">
+      <c r="F31" s="61">
         <v>3</v>
       </c>
-      <c r="G31" s="84"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="75"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B32" s="74"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="66">
+      <c r="G31" s="76"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="67"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="65"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="78"/>
+      <c r="Q31" s="78"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="65"/>
+      <c r="T31" s="65"/>
+      <c r="U31" s="67"/>
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="B32" s="66"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="61">
         <v>5</v>
       </c>
-      <c r="F32" s="66">
+      <c r="F32" s="61">
         <v>3</v>
       </c>
-      <c r="G32" s="84"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="75"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B33" s="74"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="66">
+      <c r="G32" s="76"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="67"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="65"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="78"/>
+      <c r="O32" s="131" t="s">
+        <v>374</v>
+      </c>
+      <c r="P32" s="132"/>
+      <c r="Q32" s="78"/>
+      <c r="R32" s="65"/>
+      <c r="S32" s="65"/>
+      <c r="T32" s="65"/>
+      <c r="U32" s="67"/>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="B33" s="66"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="61">
         <v>6</v>
       </c>
-      <c r="F33" s="66">
+      <c r="F33" s="61">
         <v>4</v>
       </c>
-      <c r="G33" s="84"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="75"/>
-    </row>
-    <row r="34" spans="2:9" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="81"/>
-      <c r="C34" s="87" t="s">
+      <c r="G33" s="76"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="67"/>
+      <c r="K33" s="66"/>
+      <c r="L33" s="65"/>
+      <c r="M33" s="97"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="100" t="s">
+        <v>360</v>
+      </c>
+      <c r="P33" s="100"/>
+      <c r="Q33" s="100"/>
+      <c r="R33" s="98"/>
+      <c r="S33" s="65"/>
+      <c r="T33" s="65"/>
+      <c r="U33" s="67"/>
+    </row>
+    <row r="34" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B34" s="73"/>
+      <c r="C34" s="79" t="s">
         <v>355</v>
       </c>
-      <c r="D34" s="82"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="82"/>
-      <c r="H34" s="82"/>
-      <c r="I34" s="83"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
+      <c r="I34" s="75"/>
+      <c r="K34" s="66"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="99" t="s">
+        <v>375</v>
+      </c>
+      <c r="O34" s="96" t="s">
+        <v>287</v>
+      </c>
+      <c r="P34" s="96" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q34" s="96" t="s">
+        <v>297</v>
+      </c>
+      <c r="R34" s="65"/>
+      <c r="S34" s="65"/>
+      <c r="T34" s="65"/>
+      <c r="U34" s="67"/>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K35" s="66"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="78">
+        <v>1</v>
+      </c>
+      <c r="O35" s="54">
+        <v>1</v>
+      </c>
+      <c r="P35" s="54" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q35" s="54">
+        <v>2</v>
+      </c>
+      <c r="R35" s="65"/>
+      <c r="S35" s="65"/>
+      <c r="T35" s="65"/>
+      <c r="U35" s="67"/>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K36" s="66"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="78">
+        <v>2</v>
+      </c>
+      <c r="O36" s="54">
+        <v>2</v>
+      </c>
+      <c r="P36" s="54" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q36" s="54">
+        <v>3</v>
+      </c>
+      <c r="R36" s="65"/>
+      <c r="S36" s="65"/>
+      <c r="T36" s="65"/>
+      <c r="U36" s="67"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K37" s="66"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="78">
+        <v>3</v>
+      </c>
+      <c r="O37" s="54">
+        <v>1</v>
+      </c>
+      <c r="P37" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q37" s="54">
+        <v>2</v>
+      </c>
+      <c r="R37" s="65"/>
+      <c r="S37" s="65"/>
+      <c r="T37" s="65"/>
+      <c r="U37" s="67"/>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K38" s="66"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="78">
+        <v>4</v>
+      </c>
+      <c r="O38" s="54">
+        <v>1</v>
+      </c>
+      <c r="P38" s="54" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q38" s="54">
+        <v>2</v>
+      </c>
+      <c r="R38" s="65"/>
+      <c r="S38" s="65"/>
+      <c r="T38" s="65"/>
+      <c r="U38" s="67"/>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K39" s="66"/>
+      <c r="L39" s="65"/>
+      <c r="M39" s="65"/>
+      <c r="N39" s="78">
+        <v>5</v>
+      </c>
+      <c r="O39" s="54">
+        <v>2</v>
+      </c>
+      <c r="P39" s="54" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q39" s="54">
+        <v>1</v>
+      </c>
+      <c r="R39" s="65"/>
+      <c r="S39" s="65"/>
+      <c r="T39" s="65"/>
+      <c r="U39" s="67"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K40" s="66"/>
+      <c r="L40" s="65"/>
+      <c r="M40" s="65"/>
+      <c r="N40" s="78">
+        <v>6</v>
+      </c>
+      <c r="O40" s="54">
+        <v>3</v>
+      </c>
+      <c r="P40" s="54" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q40" s="54">
+        <v>1</v>
+      </c>
+      <c r="R40" s="65"/>
+      <c r="S40" s="65"/>
+      <c r="T40" s="65"/>
+      <c r="U40" s="67"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K41" s="66"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
+      <c r="N41" s="78">
+        <v>7</v>
+      </c>
+      <c r="O41" s="54">
+        <v>3</v>
+      </c>
+      <c r="P41" s="54" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q41" s="54">
+        <v>1</v>
+      </c>
+      <c r="R41" s="65"/>
+      <c r="S41" s="65"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="67"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K42" s="66"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="65"/>
+      <c r="N42" s="78">
+        <v>8</v>
+      </c>
+      <c r="O42" s="54">
+        <v>4</v>
+      </c>
+      <c r="P42" s="54" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q42" s="54">
+        <v>1</v>
+      </c>
+      <c r="R42" s="65"/>
+      <c r="S42" s="65"/>
+      <c r="T42" s="65"/>
+      <c r="U42" s="67"/>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K43" s="66"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="78">
+        <v>9</v>
+      </c>
+      <c r="O43" s="54">
+        <v>4</v>
+      </c>
+      <c r="P43" s="54" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q43" s="54">
+        <v>2</v>
+      </c>
+      <c r="R43" s="65"/>
+      <c r="S43" s="65"/>
+      <c r="T43" s="65"/>
+      <c r="U43" s="67"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K44" s="66"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="78">
+        <v>10</v>
+      </c>
+      <c r="O44" s="54">
+        <v>4</v>
+      </c>
+      <c r="P44" s="54" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q44" s="54">
+        <v>2</v>
+      </c>
+      <c r="R44" s="65"/>
+      <c r="S44" s="65"/>
+      <c r="T44" s="65"/>
+      <c r="U44" s="67"/>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K45" s="66"/>
+      <c r="L45" s="65"/>
+      <c r="M45" s="65"/>
+      <c r="N45" s="78">
+        <v>11</v>
+      </c>
+      <c r="O45" s="54">
+        <v>1</v>
+      </c>
+      <c r="P45" s="54" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q45" s="54">
+        <v>3</v>
+      </c>
+      <c r="R45" s="65"/>
+      <c r="S45" s="65"/>
+      <c r="T45" s="65"/>
+      <c r="U45" s="67"/>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.45">
+      <c r="K46" s="66"/>
+      <c r="L46" s="65"/>
+      <c r="M46" s="65"/>
+      <c r="N46" s="78">
+        <v>12</v>
+      </c>
+      <c r="O46" s="54">
+        <v>2</v>
+      </c>
+      <c r="P46" s="54" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q46" s="54">
+        <v>2</v>
+      </c>
+      <c r="R46" s="65" t="s">
+        <v>377</v>
+      </c>
+      <c r="S46" s="65"/>
+      <c r="T46" s="65"/>
+      <c r="U46" s="67"/>
+    </row>
+    <row r="47" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K47" s="73"/>
+      <c r="L47" s="74"/>
+      <c r="M47" s="74"/>
+      <c r="N47" s="74"/>
+      <c r="O47" s="74"/>
+      <c r="P47" s="74"/>
+      <c r="Q47" s="74"/>
+      <c r="R47" s="74"/>
+      <c r="S47" s="74"/>
+      <c r="T47" s="74"/>
+      <c r="U47" s="75"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="7">
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="K2:U2"/>
+    <mergeCell ref="W2:AE2"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:N250"/>
-  <sheetFormatPr defaultColWidth="16.6875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:R64"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="15.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.6875" style="29"/>
-    <col min="2" max="2" width="30.3125" style="29" customWidth="1"/>
-    <col min="3" max="3" width="25.875" style="29" customWidth="1"/>
-    <col min="4" max="4" width="30.125" style="29" customWidth="1"/>
-    <col min="5" max="5" width="27.3125" style="29" customWidth="1"/>
-    <col min="6" max="6" width="26.875" style="29" customWidth="1"/>
-    <col min="7" max="7" width="32.5625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="29" style="29" customWidth="1"/>
-    <col min="9" max="9" width="45.125" style="29" customWidth="1"/>
-    <col min="10" max="10" width="25.3125" style="29" customWidth="1"/>
-    <col min="11" max="11" width="29" style="29" customWidth="1"/>
-    <col min="12" max="12" width="16.6875" style="29"/>
-    <col min="13" max="13" width="28.125" style="29" customWidth="1"/>
-    <col min="14" max="14" width="23.3125" style="29" customWidth="1"/>
-    <col min="15" max="16384" width="16.6875" style="29"/>
+    <col min="1" max="1" width="14.6640625" style="52" customWidth="1"/>
+    <col min="2" max="3" width="28.19921875" style="52" customWidth="1"/>
+    <col min="4" max="4" width="51" style="52" customWidth="1"/>
+    <col min="5" max="5" width="34.3984375" style="52" customWidth="1"/>
+    <col min="6" max="7" width="27.1328125" style="52" customWidth="1"/>
+    <col min="8" max="9" width="28.6640625" style="52" customWidth="1"/>
+    <col min="10" max="10" width="33.33203125" style="52" customWidth="1"/>
+    <col min="11" max="11" width="27.53125" style="52" customWidth="1"/>
+    <col min="12" max="12" width="24.53125" style="52" customWidth="1"/>
+    <col min="13" max="13" width="28.53125" style="52" customWidth="1"/>
+    <col min="14" max="14" width="17.86328125" style="52" customWidth="1"/>
+    <col min="15" max="16" width="28.1328125" style="52" customWidth="1"/>
+    <col min="17" max="17" width="27" style="52" customWidth="1"/>
+    <col min="18" max="18" width="30.53125" style="52" customWidth="1"/>
+    <col min="19" max="19" width="21.1328125" style="52" customWidth="1"/>
+    <col min="20" max="20" width="22.6640625" style="52" customWidth="1"/>
+    <col min="21" max="21" width="22.33203125" style="52" customWidth="1"/>
+    <col min="22" max="22" width="28.6640625" style="52" customWidth="1"/>
+    <col min="23" max="35" width="14.6640625" style="52" customWidth="1"/>
+    <col min="36" max="16384" width="9.1328125" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D1" s="52" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D2" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+    </row>
+    <row r="3" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="52" t="s">
+        <v>458</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>458</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="H3" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="L3" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="M3" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+    </row>
+    <row r="4" spans="2:18" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>381</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="J4" s="39" t="s">
+        <v>384</v>
+      </c>
+      <c r="K4" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="L4" s="39" t="s">
+        <v>386</v>
+      </c>
+      <c r="M4" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="N4" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="O4" s="39" t="s">
+        <v>389</v>
+      </c>
+      <c r="P4" s="39" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="102" t="s">
+        <v>437</v>
+      </c>
+      <c r="C5" s="102" t="s">
+        <v>391</v>
+      </c>
+      <c r="D5" s="102" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="102" t="s">
+        <v>359</v>
+      </c>
+      <c r="F5" s="102" t="s">
+        <v>392</v>
+      </c>
+      <c r="G5" s="102" t="s">
+        <v>393</v>
+      </c>
+      <c r="H5" s="102" t="s">
+        <v>403</v>
+      </c>
+      <c r="I5" s="102" t="s">
+        <v>486</v>
+      </c>
+      <c r="J5" s="102" t="s">
+        <v>394</v>
+      </c>
+      <c r="K5" s="102" t="s">
+        <v>395</v>
+      </c>
+      <c r="L5" s="102" t="s">
+        <v>396</v>
+      </c>
+      <c r="M5" s="102" t="s">
+        <v>397</v>
+      </c>
+      <c r="N5" s="102" t="s">
+        <v>398</v>
+      </c>
+      <c r="O5" s="102" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" s="102" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="40" t="s">
+        <v>438</v>
+      </c>
+      <c r="C6" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>358</v>
+      </c>
+      <c r="F6" s="104" t="s">
+        <v>401</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="H6" s="102" t="s">
+        <v>415</v>
+      </c>
+      <c r="I6" s="40" t="s">
+        <v>404</v>
+      </c>
+      <c r="J6" s="82" t="s">
+        <v>405</v>
+      </c>
+      <c r="K6" s="40" t="s">
+        <v>406</v>
+      </c>
+      <c r="L6" s="40" t="s">
+        <v>407</v>
+      </c>
+      <c r="M6" s="40" t="s">
+        <v>408</v>
+      </c>
+      <c r="N6" s="40" t="s">
+        <v>409</v>
+      </c>
+      <c r="O6" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="P6" s="40" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="40" t="s">
+        <v>439</v>
+      </c>
+      <c r="C7" s="103" t="s">
+        <v>412</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="40"/>
+      <c r="F7" s="104" t="s">
+        <v>413</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>414</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>424</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>416</v>
+      </c>
+      <c r="J7" s="40" t="s">
+        <v>417</v>
+      </c>
+      <c r="K7" s="40" t="s">
+        <v>418</v>
+      </c>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40" t="s">
+        <v>419</v>
+      </c>
+      <c r="P7" s="42" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="40"/>
+      <c r="C8" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="D8" s="81"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="104" t="s">
+        <v>422</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>423</v>
+      </c>
+      <c r="H8" s="105"/>
+      <c r="I8" s="40" t="s">
+        <v>425</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>426</v>
+      </c>
+      <c r="K8" s="40" t="s">
+        <v>427</v>
+      </c>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40" t="s">
+        <v>428</v>
+      </c>
+      <c r="P8" s="42" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q8" s="25"/>
+    </row>
+    <row r="9" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="40"/>
+      <c r="C9" s="40" t="s">
+        <v>429</v>
+      </c>
+      <c r="D9" s="40"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="40" t="s">
+        <v>430</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>477</v>
+      </c>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40" t="s">
+        <v>487</v>
+      </c>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40" t="s">
+        <v>431</v>
+      </c>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="40"/>
+      <c r="C10" s="106" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40" t="s">
+        <v>432</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="H10" s="41"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40" t="s">
+        <v>434</v>
+      </c>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H11" s="40"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="28" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q11" s="17"/>
+    </row>
+    <row r="12" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="101"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="81"/>
+      <c r="O13" s="81"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="81"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="81"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="81"/>
+      <c r="O15" s="81"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H17" s="80"/>
+    </row>
+    <row r="18" spans="4:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I18" s="80"/>
+    </row>
+    <row r="19" spans="4:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H19" s="81"/>
+    </row>
+    <row r="20" spans="4:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D20" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="I20" s="81"/>
+    </row>
+    <row r="21" spans="4:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D21" s="80" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="83"/>
+      <c r="J21" s="80"/>
+      <c r="L21" s="128"/>
+      <c r="M21" s="128"/>
+      <c r="N21" s="128"/>
+    </row>
+    <row r="22" spans="4:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="I22" s="83"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+    </row>
+    <row r="23" spans="4:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D23" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="80"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="80"/>
+      <c r="J23" s="81"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+    </row>
+    <row r="24" spans="4:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="80"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+    </row>
+    <row r="25" spans="4:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D25" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="80"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="83"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+    </row>
+    <row r="26" spans="4:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D26" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="I26" s="81"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+    </row>
+    <row r="27" spans="4:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D27" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="80"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="80"/>
+      <c r="J27" s="80"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="4:16" ht="44.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D28" s="80" t="s">
+        <v>337</v>
+      </c>
+      <c r="E28" s="80"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" spans="4:16" ht="57.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D29" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="80"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="41"/>
+    </row>
+    <row r="30" spans="4:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H30" s="11"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+    </row>
+    <row r="31" spans="4:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I31" s="11"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+    </row>
+    <row r="32" spans="4:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D32" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="10"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
+    </row>
+    <row r="33" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D33" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+    </row>
+    <row r="34" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D34" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+    </row>
+    <row r="35" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D35" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="21"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="53"/>
+    </row>
+    <row r="36" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D36" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D37" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" s="9"/>
+      <c r="L37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D38" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D39" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E39" s="10"/>
+    </row>
+    <row r="40" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D41" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+    </row>
+    <row r="42" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D42" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" s="10"/>
+    </row>
+    <row r="43" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D43" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="10"/>
+    </row>
+    <row r="44" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D44" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" s="10"/>
+    </row>
+    <row r="45" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="46" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="47" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D47" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="H47" s="11"/>
+    </row>
+    <row r="48" spans="4:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D48" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+    </row>
+    <row r="49" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+    </row>
+    <row r="50" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+    </row>
+    <row r="51" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D51" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+    </row>
+    <row r="52" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D52" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" s="24"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+    </row>
+    <row r="53" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+    </row>
+    <row r="54" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+    </row>
+    <row r="55" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D55" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+    </row>
+    <row r="56" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D56" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E56" s="24"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+    </row>
+    <row r="57" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="58" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="59" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="60" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="63" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="64" spans="4:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L21:N21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I204"/>
+  <sheetFormatPr defaultColWidth="24.59765625" defaultRowHeight="28.05" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="2" width="24.59765625" style="82"/>
+    <col min="3" max="3" width="34.265625" style="82" customWidth="1"/>
+    <col min="4" max="5" width="24.59765625" style="82"/>
+    <col min="6" max="6" width="45.1328125" style="82" customWidth="1"/>
+    <col min="7" max="7" width="27.06640625" style="82" customWidth="1"/>
+    <col min="8" max="16384" width="24.59765625" style="82"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="107" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="108" t="s">
+        <v>437</v>
+      </c>
+      <c r="C3" s="109" t="s">
+        <v>438</v>
+      </c>
+      <c r="D3" s="110" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="111">
+        <v>1</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>440</v>
+      </c>
+      <c r="D4" s="113">
+        <v>10269</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="111">
+        <v>2</v>
+      </c>
+      <c r="C5" s="112" t="s">
+        <v>441</v>
+      </c>
+      <c r="D5" s="113">
+        <v>10277</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="111">
+        <v>3</v>
+      </c>
+      <c r="C6" s="112" t="s">
+        <v>442</v>
+      </c>
+      <c r="D6" s="113">
+        <v>10259</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="111">
+        <v>4</v>
+      </c>
+      <c r="C7" s="112" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" s="113">
+        <v>10233</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="114">
+        <v>5</v>
+      </c>
+      <c r="C8" s="115" t="s">
+        <v>444</v>
+      </c>
+      <c r="D8" s="116">
+        <v>10211</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B11" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="84"/>
+    </row>
+    <row r="12" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="108" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="85">
+        <v>1</v>
+      </c>
+      <c r="C13" s="85" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="85">
+        <v>2</v>
+      </c>
+      <c r="C14" s="85" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="85">
+        <v>3</v>
+      </c>
+      <c r="C15" s="85" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="85">
+        <v>4</v>
+      </c>
+      <c r="C16" s="85" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="85">
+        <v>5</v>
+      </c>
+      <c r="C17" s="85" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="85">
+        <v>6</v>
+      </c>
+      <c r="C18" s="85" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="85">
+        <v>7</v>
+      </c>
+      <c r="C19" s="85" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+    </row>
+    <row r="23" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="108" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="85">
+        <v>1</v>
+      </c>
+      <c r="C24" s="85" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="85">
+        <v>2</v>
+      </c>
+      <c r="C25" s="85" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="85">
+        <v>3</v>
+      </c>
+      <c r="C26" s="85" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="85">
+        <v>4</v>
+      </c>
+      <c r="C27" s="85" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="85">
+        <v>5</v>
+      </c>
+      <c r="C28" s="85" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B29" s="85">
+        <v>6</v>
+      </c>
+      <c r="C29" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="85">
+        <v>7</v>
+      </c>
+      <c r="C30" s="85" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="85">
+        <v>8</v>
+      </c>
+      <c r="C31" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="85">
+        <v>9</v>
+      </c>
+      <c r="C32" s="85" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B33" s="85">
+        <v>10</v>
+      </c>
+      <c r="C33" s="85" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" s="85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="85">
+        <v>11</v>
+      </c>
+      <c r="C34" s="85" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" s="85">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="85">
+        <v>12</v>
+      </c>
+      <c r="C35" s="85" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B36" s="85">
+        <v>13</v>
+      </c>
+      <c r="C36" s="85" t="s">
+        <v>145</v>
+      </c>
+      <c r="D36" s="85">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B37" s="85">
+        <v>14</v>
+      </c>
+      <c r="C37" s="85" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="85">
+        <v>15</v>
+      </c>
+      <c r="C38" s="85" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="85">
+        <v>16</v>
+      </c>
+      <c r="C39" s="85" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" s="85">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B40" s="85">
+        <v>17</v>
+      </c>
+      <c r="C40" s="85" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" s="85">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B41" s="85">
+        <v>18</v>
+      </c>
+      <c r="C41" s="85" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="85">
+        <v>19</v>
+      </c>
+      <c r="C42" s="85" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" s="85">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="85">
+        <v>20</v>
+      </c>
+      <c r="C43" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="85">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="46" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="117" t="s">
+        <v>379</v>
+      </c>
+      <c r="C46" s="118" t="s">
+        <v>350</v>
+      </c>
+      <c r="D46" s="118" t="s">
+        <v>350</v>
+      </c>
+      <c r="E46" s="118"/>
+      <c r="F46" s="118" t="s">
+        <v>460</v>
+      </c>
+      <c r="G46" s="119"/>
+    </row>
+    <row r="47" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B47" s="120" t="s">
+        <v>391</v>
+      </c>
+      <c r="C47" s="103" t="s">
+        <v>400</v>
+      </c>
+      <c r="D47" s="103" t="s">
+        <v>412</v>
+      </c>
+      <c r="E47" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="F47" s="103" t="s">
+        <v>429</v>
+      </c>
+      <c r="G47" s="121" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B48" s="111" t="s">
+        <v>445</v>
+      </c>
+      <c r="C48" s="112" t="s">
+        <v>450</v>
+      </c>
+      <c r="D48" s="112">
+        <v>1</v>
+      </c>
+      <c r="E48" s="112" t="s">
+        <v>446</v>
+      </c>
+      <c r="F48" s="112" t="s">
+        <v>451</v>
+      </c>
+      <c r="G48" s="113" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B49" s="111"/>
+      <c r="C49" s="112" t="s">
+        <v>452</v>
+      </c>
+      <c r="D49" s="112">
+        <v>2</v>
+      </c>
+      <c r="E49" s="112" t="s">
+        <v>447</v>
+      </c>
+      <c r="F49" s="112" t="s">
+        <v>448</v>
+      </c>
+      <c r="G49" s="113" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B50" s="111"/>
+      <c r="C50" s="112" t="s">
+        <v>453</v>
+      </c>
+      <c r="D50" s="112">
+        <v>3</v>
+      </c>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112" t="s">
+        <v>454</v>
+      </c>
+      <c r="G50" s="113"/>
+    </row>
+    <row r="51" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B51" s="111"/>
+      <c r="C51" s="112" t="s">
+        <v>455</v>
+      </c>
+      <c r="D51" s="112">
+        <v>4</v>
+      </c>
+      <c r="E51" s="112"/>
+      <c r="F51" s="122" t="s">
+        <v>449</v>
+      </c>
+      <c r="G51" s="113"/>
+    </row>
+    <row r="52" spans="2:7" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B52" s="114"/>
+      <c r="C52" s="115" t="s">
+        <v>456</v>
+      </c>
+      <c r="D52" s="115">
+        <v>5</v>
+      </c>
+      <c r="E52" s="115"/>
+      <c r="F52" s="115"/>
+      <c r="G52" s="116"/>
+    </row>
+    <row r="55" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B55" s="39" t="s">
+        <v>389</v>
+      </c>
+      <c r="C55" s="84"/>
+      <c r="D55" s="84"/>
+      <c r="E55" s="84"/>
+    </row>
+    <row r="56" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B56" s="102" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>419</v>
+      </c>
+      <c r="E56" s="40" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B57" s="85">
+        <v>1</v>
+      </c>
+      <c r="C57" s="85" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="85">
+        <v>0</v>
+      </c>
+      <c r="E57" s="85" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B58" s="85">
+        <v>2</v>
+      </c>
+      <c r="C58" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="85">
+        <v>0</v>
+      </c>
+      <c r="E58" s="85" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B59" s="85">
+        <v>3</v>
+      </c>
+      <c r="C59" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="85">
+        <v>0</v>
+      </c>
+      <c r="E59" s="85" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B60" s="85">
+        <v>4</v>
+      </c>
+      <c r="C60" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="85">
+        <v>0</v>
+      </c>
+      <c r="E60" s="85" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B61" s="85">
+        <v>5</v>
+      </c>
+      <c r="C61" s="85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="85">
+        <v>0</v>
+      </c>
+      <c r="E61" s="85" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B62" s="85">
+        <v>6</v>
+      </c>
+      <c r="C62" s="85" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="85">
+        <v>1</v>
+      </c>
+      <c r="E62" s="85" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B63" s="85">
+        <v>7</v>
+      </c>
+      <c r="C63" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="85">
+        <v>1</v>
+      </c>
+      <c r="E63" s="85" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B64" s="85">
+        <v>8</v>
+      </c>
+      <c r="C64" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="85">
+        <v>1</v>
+      </c>
+      <c r="E64" s="85" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B65" s="85">
+        <v>9</v>
+      </c>
+      <c r="C65" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="85">
+        <v>1</v>
+      </c>
+      <c r="E65" s="85" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B66" s="85">
+        <v>10</v>
+      </c>
+      <c r="C66" s="85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="85">
+        <v>1</v>
+      </c>
+      <c r="E66" s="85" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="69" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B69" s="117" t="s">
+        <v>380</v>
+      </c>
+      <c r="C69" s="118"/>
+      <c r="D69" s="118"/>
+      <c r="E69" s="118" t="s">
+        <v>496</v>
+      </c>
+      <c r="F69" s="118"/>
+      <c r="G69" s="119"/>
+    </row>
+    <row r="70" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B70" s="120" t="s">
+        <v>392</v>
+      </c>
+      <c r="C70" s="104" t="s">
+        <v>401</v>
+      </c>
+      <c r="D70" s="104" t="s">
+        <v>413</v>
+      </c>
+      <c r="E70" s="104" t="s">
+        <v>422</v>
+      </c>
+      <c r="F70" s="40" t="s">
+        <v>430</v>
+      </c>
+      <c r="G70" s="124" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B71" s="111" t="s">
+        <v>459</v>
+      </c>
+      <c r="C71" s="112"/>
+      <c r="D71" s="112"/>
+      <c r="E71" s="112"/>
+      <c r="F71" s="112"/>
+      <c r="G71" s="113"/>
+    </row>
+    <row r="72" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B72" s="111"/>
+      <c r="C72" s="139" t="s">
+        <v>497</v>
+      </c>
+      <c r="D72" s="140"/>
+      <c r="E72" s="140"/>
+      <c r="F72" s="140"/>
+      <c r="G72" s="113"/>
+    </row>
+    <row r="73" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B73" s="111"/>
+      <c r="C73" s="140"/>
+      <c r="D73" s="140"/>
+      <c r="E73" s="140"/>
+      <c r="F73" s="140"/>
+      <c r="G73" s="113"/>
+    </row>
+    <row r="74" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B74" s="111"/>
+      <c r="C74" s="140"/>
+      <c r="D74" s="140"/>
+      <c r="E74" s="140"/>
+      <c r="F74" s="140"/>
+      <c r="G74" s="113"/>
+    </row>
+    <row r="75" spans="2:7" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B75" s="114"/>
+      <c r="C75" s="141"/>
+      <c r="D75" s="141"/>
+      <c r="E75" s="141"/>
+      <c r="F75" s="141"/>
+      <c r="G75" s="116"/>
+    </row>
+    <row r="77" spans="2:7" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="78" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B78" s="117" t="s">
+        <v>386</v>
+      </c>
+      <c r="C78" s="119"/>
+    </row>
+    <row r="79" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B79" s="120" t="s">
+        <v>396</v>
+      </c>
+      <c r="C79" s="124" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B80" s="111">
+        <v>1</v>
+      </c>
+      <c r="C80" s="113" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B81" s="111">
+        <v>2</v>
+      </c>
+      <c r="C81" s="113" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B82" s="114">
+        <v>3</v>
+      </c>
+      <c r="C82" s="116" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B85" s="39" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B86" s="102" t="s">
+        <v>395</v>
+      </c>
+      <c r="C86" s="40" t="s">
+        <v>406</v>
+      </c>
+      <c r="D86" s="40" t="s">
+        <v>418</v>
+      </c>
+      <c r="E86" s="40" t="s">
+        <v>427</v>
+      </c>
+      <c r="F86" s="40" t="s">
+        <v>431</v>
+      </c>
+      <c r="G86" s="40" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B87" s="85">
+        <v>1</v>
+      </c>
+      <c r="C87" s="85" t="s">
+        <v>464</v>
+      </c>
+      <c r="D87" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="E87" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F87" s="85" t="s">
+        <v>177</v>
+      </c>
+      <c r="G87" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B88" s="85">
+        <v>2</v>
+      </c>
+      <c r="C88" s="85" t="s">
+        <v>465</v>
+      </c>
+      <c r="D88" s="85" t="s">
+        <v>158</v>
+      </c>
+      <c r="E88" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F88" s="85" t="s">
+        <v>178</v>
+      </c>
+      <c r="G88" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B89" s="85">
+        <v>3</v>
+      </c>
+      <c r="C89" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="D89" s="85" t="s">
+        <v>159</v>
+      </c>
+      <c r="E89" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F89" s="85" t="s">
+        <v>179</v>
+      </c>
+      <c r="G89" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B90" s="85">
+        <v>4</v>
+      </c>
+      <c r="C90" s="85" t="s">
+        <v>467</v>
+      </c>
+      <c r="D90" s="85" t="s">
+        <v>160</v>
+      </c>
+      <c r="E90" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F90" s="85" t="s">
+        <v>180</v>
+      </c>
+      <c r="G90" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B91" s="85">
+        <v>5</v>
+      </c>
+      <c r="C91" s="85" t="s">
+        <v>468</v>
+      </c>
+      <c r="D91" s="85" t="s">
+        <v>161</v>
+      </c>
+      <c r="E91" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F91" s="85" t="s">
+        <v>181</v>
+      </c>
+      <c r="G91" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B92" s="85">
+        <v>6</v>
+      </c>
+      <c r="C92" s="85" t="s">
+        <v>469</v>
+      </c>
+      <c r="D92" s="85" t="s">
+        <v>162</v>
+      </c>
+      <c r="E92" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F92" s="85" t="s">
+        <v>182</v>
+      </c>
+      <c r="G92" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B93" s="85">
+        <v>7</v>
+      </c>
+      <c r="C93" s="85" t="s">
+        <v>470</v>
+      </c>
+      <c r="D93" s="85" t="s">
+        <v>163</v>
+      </c>
+      <c r="E93" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F93" s="85" t="s">
+        <v>183</v>
+      </c>
+      <c r="G93" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B94" s="85">
+        <v>8</v>
+      </c>
+      <c r="C94" s="85" t="s">
+        <v>471</v>
+      </c>
+      <c r="D94" s="85" t="s">
+        <v>164</v>
+      </c>
+      <c r="E94" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F94" s="85" t="s">
+        <v>184</v>
+      </c>
+      <c r="G94" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B95" s="85">
+        <v>9</v>
+      </c>
+      <c r="C95" s="85" t="s">
+        <v>472</v>
+      </c>
+      <c r="D95" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="E95" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F95" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="G95" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B96" s="85">
+        <v>10</v>
+      </c>
+      <c r="C96" s="85" t="s">
+        <v>473</v>
+      </c>
+      <c r="D96" s="85" t="s">
+        <v>166</v>
+      </c>
+      <c r="E96" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="F96" s="85" t="s">
+        <v>186</v>
+      </c>
+      <c r="G96" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="99" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B99" s="117" t="s">
+        <v>381</v>
+      </c>
+      <c r="C99" s="118"/>
+      <c r="D99" s="118"/>
+      <c r="E99" s="118"/>
+      <c r="F99" s="118"/>
+      <c r="G99" s="118"/>
+      <c r="H99" s="119"/>
+    </row>
+    <row r="100" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B100" s="120" t="s">
+        <v>393</v>
+      </c>
+      <c r="C100" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="D100" s="40" t="s">
+        <v>414</v>
+      </c>
+      <c r="E100" s="40" t="s">
+        <v>423</v>
+      </c>
+      <c r="F100" s="28" t="s">
+        <v>477</v>
+      </c>
+      <c r="G100" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="H100" s="123" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B101" s="111" t="s">
+        <v>474</v>
+      </c>
+      <c r="C101" s="112" t="s">
+        <v>475</v>
+      </c>
+      <c r="D101" s="112">
+        <v>9822299222</v>
+      </c>
+      <c r="E101" s="112" t="s">
+        <v>476</v>
+      </c>
+      <c r="F101" s="112" t="s">
+        <v>478</v>
+      </c>
+      <c r="G101" s="112" t="s">
+        <v>479</v>
+      </c>
+      <c r="H101" s="113" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B102" s="111"/>
+      <c r="C102" s="112"/>
+      <c r="D102" s="112"/>
+      <c r="E102" s="112"/>
+      <c r="F102" s="112"/>
+      <c r="G102" s="112"/>
+      <c r="H102" s="113" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B103" s="114"/>
+      <c r="C103" s="115"/>
+      <c r="D103" s="115"/>
+      <c r="E103" s="115"/>
+      <c r="F103" s="115"/>
+      <c r="G103" s="115"/>
+      <c r="H103" s="116" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="106" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B106" s="117" t="s">
+        <v>382</v>
+      </c>
+      <c r="C106" s="84"/>
+      <c r="D106" s="84"/>
+    </row>
+    <row r="107" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B107" s="120" t="s">
+        <v>403</v>
+      </c>
+      <c r="C107" s="120" t="s">
+        <v>415</v>
+      </c>
+      <c r="D107" s="40" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B108" s="142" t="s">
+        <v>258</v>
+      </c>
+      <c r="C108" s="142"/>
+      <c r="D108" s="142"/>
+    </row>
+    <row r="109" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B109" s="142"/>
+      <c r="C109" s="142"/>
+      <c r="D109" s="142"/>
+    </row>
+    <row r="110" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B110" s="142"/>
+      <c r="C110" s="142"/>
+      <c r="D110" s="142"/>
+    </row>
+    <row r="111" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B111" s="84">
+        <v>1</v>
+      </c>
+      <c r="C111" s="84">
+        <v>1</v>
+      </c>
+      <c r="D111" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B112" s="84">
+        <v>1</v>
+      </c>
+      <c r="C112" s="84">
+        <v>3</v>
+      </c>
+      <c r="D112" s="84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B113" s="84">
+        <v>2</v>
+      </c>
+      <c r="C113" s="84">
+        <v>4</v>
+      </c>
+      <c r="D113" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B114" s="84">
+        <v>2</v>
+      </c>
+      <c r="C114" s="84">
+        <v>5</v>
+      </c>
+      <c r="D114" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B115" s="84">
+        <v>3</v>
+      </c>
+      <c r="C115" s="84">
+        <v>6</v>
+      </c>
+      <c r="D115" s="84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B116" s="84">
+        <v>3</v>
+      </c>
+      <c r="C116" s="84">
+        <v>2</v>
+      </c>
+      <c r="D116" s="84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B117" s="84">
+        <v>4</v>
+      </c>
+      <c r="C117" s="84">
+        <v>8</v>
+      </c>
+      <c r="D117" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B118" s="84">
+        <v>4</v>
+      </c>
+      <c r="C118" s="84">
+        <v>12</v>
+      </c>
+      <c r="D118" s="84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B119" s="84">
+        <v>5</v>
+      </c>
+      <c r="C119" s="84">
+        <v>88</v>
+      </c>
+      <c r="D119" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B120" s="84">
+        <v>5</v>
+      </c>
+      <c r="C120" s="84">
+        <v>22</v>
+      </c>
+      <c r="D120" s="84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B121" s="84">
+        <v>5</v>
+      </c>
+      <c r="C121" s="84">
+        <v>11</v>
+      </c>
+      <c r="D121" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B122" s="84">
+        <v>5</v>
+      </c>
+      <c r="C122" s="84">
+        <v>33</v>
+      </c>
+      <c r="D122" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B123" s="84">
+        <v>6</v>
+      </c>
+      <c r="C123" s="84">
+        <v>2</v>
+      </c>
+      <c r="D123" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B124" s="84">
+        <v>7</v>
+      </c>
+      <c r="C124" s="84">
+        <v>1</v>
+      </c>
+      <c r="D124" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B125" s="84">
+        <v>8</v>
+      </c>
+      <c r="C125" s="84">
+        <v>27</v>
+      </c>
+      <c r="D125" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B126" s="84">
+        <v>8</v>
+      </c>
+      <c r="C126" s="84">
+        <v>23</v>
+      </c>
+      <c r="D126" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B127" s="84">
+        <v>8</v>
+      </c>
+      <c r="C127" s="84">
+        <v>98</v>
+      </c>
+      <c r="D127" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B128" s="84">
+        <v>9</v>
+      </c>
+      <c r="C128" s="84">
+        <v>100</v>
+      </c>
+      <c r="D128" s="84">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B129" s="84">
+        <v>9</v>
+      </c>
+      <c r="C129" s="84">
+        <v>11</v>
+      </c>
+      <c r="D129" s="84">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B130" s="84">
+        <v>9</v>
+      </c>
+      <c r="C130" s="84">
+        <v>45</v>
+      </c>
+      <c r="D130" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B131" s="84">
+        <v>9</v>
+      </c>
+      <c r="C131" s="84">
+        <v>22</v>
+      </c>
+      <c r="D131" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B132" s="84">
+        <v>9</v>
+      </c>
+      <c r="C132" s="84">
+        <v>32</v>
+      </c>
+      <c r="D132" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B133" s="84">
+        <v>10</v>
+      </c>
+      <c r="C133" s="84">
+        <v>18</v>
+      </c>
+      <c r="D133" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B134" s="84">
+        <v>10</v>
+      </c>
+      <c r="C134" s="84">
+        <v>29</v>
+      </c>
+      <c r="D134" s="84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B135" s="84">
+        <v>11</v>
+      </c>
+      <c r="C135" s="84">
+        <v>33</v>
+      </c>
+      <c r="D135" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B136" s="84">
+        <v>11</v>
+      </c>
+      <c r="C136" s="84">
+        <v>65</v>
+      </c>
+      <c r="D136" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B137" s="84">
+        <v>11</v>
+      </c>
+      <c r="C137" s="84">
+        <v>1</v>
+      </c>
+      <c r="D137" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B138" s="84">
+        <v>11</v>
+      </c>
+      <c r="C138" s="84">
+        <v>2</v>
+      </c>
+      <c r="D138" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B139" s="84">
+        <v>11</v>
+      </c>
+      <c r="C139" s="84">
+        <v>5</v>
+      </c>
+      <c r="D139" s="84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B140" s="84">
+        <v>11</v>
+      </c>
+      <c r="C140" s="84">
+        <v>7</v>
+      </c>
+      <c r="D140" s="84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B141" s="84">
+        <v>12</v>
+      </c>
+      <c r="C141" s="84">
+        <v>55</v>
+      </c>
+      <c r="D141" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B142" s="84">
+        <v>13</v>
+      </c>
+      <c r="C142" s="84">
+        <v>92</v>
+      </c>
+      <c r="D142" s="84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B143" s="84">
+        <v>13</v>
+      </c>
+      <c r="C143" s="84">
+        <v>14</v>
+      </c>
+      <c r="D143" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B144" s="82">
+        <v>14</v>
+      </c>
+      <c r="C144" s="82">
+        <v>5</v>
+      </c>
+      <c r="D144" s="82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B145" s="82">
+        <v>14</v>
+      </c>
+      <c r="C145" s="82">
+        <v>7</v>
+      </c>
+      <c r="D145" s="82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B146" s="82">
+        <v>14</v>
+      </c>
+      <c r="C146" s="82">
+        <v>2</v>
+      </c>
+      <c r="D146" s="82">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B147" s="82">
+        <v>15</v>
+      </c>
+      <c r="C147" s="82">
+        <v>9</v>
+      </c>
+      <c r="D147" s="82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B148" s="82">
+        <v>15</v>
+      </c>
+      <c r="C148" s="82">
+        <v>44</v>
+      </c>
+      <c r="D148" s="82">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B149" s="82">
+        <v>15</v>
+      </c>
+      <c r="C149" s="82">
+        <v>23</v>
+      </c>
+      <c r="D149" s="82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B150" s="82">
+        <v>16</v>
+      </c>
+      <c r="C150" s="82">
+        <v>18</v>
+      </c>
+      <c r="D150" s="82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B151" s="82">
+        <v>16</v>
+      </c>
+      <c r="C151" s="82">
+        <v>66</v>
+      </c>
+      <c r="D151" s="82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B152" s="82">
+        <v>16</v>
+      </c>
+      <c r="C152" s="82">
+        <v>77</v>
+      </c>
+      <c r="D152" s="82">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B153" s="82">
+        <v>16</v>
+      </c>
+      <c r="C153" s="82">
+        <v>1</v>
+      </c>
+      <c r="D153" s="82">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B154" s="82">
+        <v>17</v>
+      </c>
+      <c r="C154" s="82">
+        <v>82</v>
+      </c>
+      <c r="D154" s="82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B155" s="82">
+        <v>18</v>
+      </c>
+      <c r="C155" s="82">
+        <v>84</v>
+      </c>
+      <c r="D155" s="82">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B156" s="82">
+        <v>18</v>
+      </c>
+      <c r="C156" s="82">
+        <v>12</v>
+      </c>
+      <c r="D156" s="82">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B157" s="82">
+        <v>19</v>
+      </c>
+      <c r="C157" s="82">
+        <v>20</v>
+      </c>
+      <c r="D157" s="82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B158" s="82">
+        <v>19</v>
+      </c>
+      <c r="C158" s="82">
+        <v>30</v>
+      </c>
+      <c r="D158" s="82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B159" s="82">
+        <v>20</v>
+      </c>
+      <c r="C159" s="82">
+        <v>100</v>
+      </c>
+      <c r="D159" s="82">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B160" s="82">
+        <v>20</v>
+      </c>
+      <c r="C160" s="82">
+        <v>70</v>
+      </c>
+      <c r="D160" s="82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B161" s="82">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B166" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="C166" s="84"/>
+      <c r="D166" s="84"/>
+      <c r="E166" s="84"/>
+    </row>
+    <row r="167" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B167" s="102" t="s">
+        <v>486</v>
+      </c>
+      <c r="C167" s="40" t="s">
+        <v>404</v>
+      </c>
+      <c r="D167" s="40" t="s">
+        <v>416</v>
+      </c>
+      <c r="E167" s="40" t="s">
+        <v>425</v>
+      </c>
+      <c r="F167" s="40" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="168" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B168" s="82" t="s">
+        <v>445</v>
+      </c>
+      <c r="C168" s="84"/>
+      <c r="D168" s="84"/>
+      <c r="E168" s="84"/>
+      <c r="F168" s="84"/>
+    </row>
+    <row r="169" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C169" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="D169" s="84"/>
+      <c r="E169" s="84" t="s">
+        <v>230</v>
+      </c>
+      <c r="F169" s="84" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C170" s="33" t="s">
+        <v>275</v>
+      </c>
+      <c r="D170" s="84"/>
+      <c r="E170" s="84" t="s">
+        <v>271</v>
+      </c>
+      <c r="F170" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C171" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D171" s="84"/>
+      <c r="E171" s="84" t="s">
+        <v>272</v>
+      </c>
+      <c r="F171" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C172" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="D172" s="84"/>
+      <c r="E172" s="84" t="s">
+        <v>273</v>
+      </c>
+      <c r="F172" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C173" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="D173" s="84"/>
+      <c r="E173" s="84" t="s">
+        <v>277</v>
+      </c>
+      <c r="F173" s="84"/>
+    </row>
+    <row r="175" spans="2:6" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="176" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B176" s="117" t="s">
+        <v>384</v>
+      </c>
+      <c r="C176" s="118"/>
+      <c r="D176" s="118"/>
+      <c r="E176" s="119"/>
+    </row>
+    <row r="177" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B177" s="120" t="s">
+        <v>394</v>
+      </c>
+      <c r="C177" s="112" t="s">
+        <v>405</v>
+      </c>
+      <c r="D177" s="40" t="s">
+        <v>417</v>
+      </c>
+      <c r="E177" s="123" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="178" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B178" s="111"/>
+      <c r="C178" s="112"/>
+      <c r="D178" s="112"/>
+      <c r="E178" s="113"/>
+    </row>
+    <row r="179" spans="2:6" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B179" s="114"/>
+      <c r="C179" s="115" t="s">
+        <v>488</v>
+      </c>
+      <c r="D179" s="115"/>
+      <c r="E179" s="116"/>
+    </row>
+    <row r="181" spans="2:6" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="182" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B182" s="117" t="s">
+        <v>387</v>
+      </c>
+      <c r="C182" s="84"/>
+      <c r="E182" s="117" t="s">
+        <v>388</v>
+      </c>
+      <c r="F182" s="84"/>
+    </row>
+    <row r="183" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B183" s="120" t="s">
+        <v>489</v>
+      </c>
+      <c r="C183" s="40" t="s">
+        <v>490</v>
+      </c>
+      <c r="E183" s="120" t="s">
+        <v>398</v>
+      </c>
+      <c r="F183" s="40" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="184" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B184" s="85">
+        <v>1</v>
+      </c>
+      <c r="C184" s="85" t="s">
+        <v>210</v>
+      </c>
+      <c r="E184" s="85">
+        <v>1</v>
+      </c>
+      <c r="F184" s="85" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="185" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B185" s="85">
+        <v>2</v>
+      </c>
+      <c r="C185" s="85" t="s">
+        <v>211</v>
+      </c>
+      <c r="E185" s="85">
+        <v>2</v>
+      </c>
+      <c r="F185" s="85" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="186" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B186" s="85">
+        <v>3</v>
+      </c>
+      <c r="C186" s="85" t="s">
+        <v>212</v>
+      </c>
+      <c r="E186" s="85">
+        <v>3</v>
+      </c>
+      <c r="F186" s="85" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="187" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B187" s="85">
+        <v>4</v>
+      </c>
+      <c r="C187" s="85" t="s">
+        <v>213</v>
+      </c>
+      <c r="E187" s="85">
+        <v>4</v>
+      </c>
+      <c r="F187" s="85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="188" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B188" s="85">
+        <v>5</v>
+      </c>
+      <c r="C188" s="85" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="189" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B189" s="85">
+        <v>6</v>
+      </c>
+      <c r="C189" s="85" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="190" spans="2:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B190" s="85">
+        <v>7</v>
+      </c>
+      <c r="C190" s="85" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="192" spans="2:6" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="193" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B193" s="117" t="s">
+        <v>390</v>
+      </c>
+      <c r="C193" s="84"/>
+      <c r="D193" s="84"/>
+      <c r="E193" s="84"/>
+      <c r="F193" s="84"/>
+      <c r="G193" s="84"/>
+      <c r="H193" s="84"/>
+      <c r="I193" s="84"/>
+    </row>
+    <row r="194" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B194" s="120" t="s">
+        <v>399</v>
+      </c>
+      <c r="C194" s="40" t="s">
+        <v>411</v>
+      </c>
+      <c r="D194" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="E194" s="40" t="s">
+        <v>492</v>
+      </c>
+      <c r="F194" s="40" t="s">
+        <v>493</v>
+      </c>
+      <c r="G194" s="40" t="s">
+        <v>494</v>
+      </c>
+      <c r="H194" s="40" t="s">
+        <v>495</v>
+      </c>
+      <c r="I194" s="103" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B195" s="85">
+        <v>1</v>
+      </c>
+      <c r="C195" s="85" t="s">
+        <v>230</v>
+      </c>
+      <c r="D195" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="E195" s="85" t="s">
+        <v>177</v>
+      </c>
+      <c r="F195" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G195" s="85" t="s">
+        <v>242</v>
+      </c>
+      <c r="H195" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I195" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B196" s="85">
+        <v>2</v>
+      </c>
+      <c r="C196" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="D196" s="85" t="s">
+        <v>241</v>
+      </c>
+      <c r="E196" s="85" t="s">
+        <v>178</v>
+      </c>
+      <c r="F196" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G196" s="85" t="s">
+        <v>243</v>
+      </c>
+      <c r="H196" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I196" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B197" s="85">
+        <v>3</v>
+      </c>
+      <c r="C197" s="85" t="s">
+        <v>233</v>
+      </c>
+      <c r="D197" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="E197" s="85" t="s">
+        <v>179</v>
+      </c>
+      <c r="F197" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G197" s="85" t="s">
+        <v>244</v>
+      </c>
+      <c r="H197" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I197" s="85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B198" s="85">
+        <v>4</v>
+      </c>
+      <c r="C198" s="85" t="s">
+        <v>232</v>
+      </c>
+      <c r="D198" s="85" t="s">
+        <v>262</v>
+      </c>
+      <c r="E198" s="85" t="s">
+        <v>180</v>
+      </c>
+      <c r="F198" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G198" s="85" t="s">
+        <v>245</v>
+      </c>
+      <c r="H198" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I198" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B199" s="85">
+        <v>5</v>
+      </c>
+      <c r="C199" s="85" t="s">
+        <v>234</v>
+      </c>
+      <c r="D199" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="E199" s="85" t="s">
+        <v>181</v>
+      </c>
+      <c r="F199" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G199" s="85" t="s">
+        <v>246</v>
+      </c>
+      <c r="H199" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I199" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B200" s="85">
+        <v>6</v>
+      </c>
+      <c r="C200" s="85" t="s">
+        <v>235</v>
+      </c>
+      <c r="D200" s="85" t="s">
+        <v>263</v>
+      </c>
+      <c r="E200" s="85" t="s">
+        <v>182</v>
+      </c>
+      <c r="F200" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G200" s="85" t="s">
+        <v>247</v>
+      </c>
+      <c r="H200" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I200" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B201" s="85">
+        <v>7</v>
+      </c>
+      <c r="C201" s="85" t="s">
+        <v>236</v>
+      </c>
+      <c r="D201" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="E201" s="85" t="s">
+        <v>183</v>
+      </c>
+      <c r="F201" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G201" s="85" t="s">
+        <v>248</v>
+      </c>
+      <c r="H201" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I201" s="85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B202" s="85">
+        <v>8</v>
+      </c>
+      <c r="C202" s="85" t="s">
+        <v>237</v>
+      </c>
+      <c r="D202" s="85" t="s">
+        <v>265</v>
+      </c>
+      <c r="E202" s="85" t="s">
+        <v>184</v>
+      </c>
+      <c r="F202" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G202" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="H202" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I202" s="85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B203" s="85">
+        <v>9</v>
+      </c>
+      <c r="C203" s="85" t="s">
+        <v>238</v>
+      </c>
+      <c r="D203" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="E203" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="F203" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G203" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="H203" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I203" s="85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B204" s="85">
+        <v>10</v>
+      </c>
+      <c r="C204" s="85" t="s">
+        <v>239</v>
+      </c>
+      <c r="D204" s="85" t="s">
+        <v>267</v>
+      </c>
+      <c r="E204" s="85" t="s">
+        <v>186</v>
+      </c>
+      <c r="F204" s="85">
+        <v>123456789</v>
+      </c>
+      <c r="G204" s="85" t="s">
+        <v>251</v>
+      </c>
+      <c r="H204" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="I204" s="85">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C72:F75"/>
+    <mergeCell ref="B108:D110"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:N250"/>
+  <sheetFormatPr defaultColWidth="16.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" style="29"/>
+    <col min="2" max="2" width="30.33203125" style="29" customWidth="1"/>
+    <col min="3" max="3" width="25.86328125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="30.1328125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="26.86328125" style="29" customWidth="1"/>
+    <col min="7" max="7" width="32.53125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="29" style="29" customWidth="1"/>
+    <col min="9" max="9" width="45.1328125" style="29" customWidth="1"/>
+    <col min="10" max="10" width="25.33203125" style="29" customWidth="1"/>
+    <col min="11" max="11" width="29" style="29" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" style="29"/>
+    <col min="13" max="13" width="28.1328125" style="29" customWidth="1"/>
+    <col min="14" max="14" width="23.33203125" style="29" customWidth="1"/>
+    <col min="15" max="16384" width="16.6640625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="34" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="13" t="s">
         <v>46</v>
       </c>
@@ -5224,7 +10186,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="30">
         <v>1</v>
       </c>
@@ -5256,7 +10218,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="30">
         <v>2</v>
       </c>
@@ -5288,7 +10250,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="30">
         <v>3</v>
       </c>
@@ -5320,7 +10282,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="30">
         <v>4</v>
       </c>
@@ -5352,7 +10314,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="30">
         <v>5</v>
       </c>
@@ -5384,7 +10346,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="30">
         <v>6</v>
       </c>
@@ -5410,7 +10372,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="30">
         <v>7</v>
       </c>
@@ -5436,7 +10398,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="30">
         <v>8</v>
       </c>
@@ -5462,7 +10424,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="30">
         <v>9</v>
       </c>
@@ -5476,7 +10438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="30">
         <v>10</v>
       </c>
@@ -5496,7 +10458,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="30">
         <v>11</v>
       </c>
@@ -5528,7 +10490,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="30">
         <v>12</v>
       </c>
@@ -5560,7 +10522,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="17" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="30">
         <v>13</v>
       </c>
@@ -5592,7 +10554,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="30">
         <v>14</v>
       </c>
@@ -5624,7 +10586,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="19" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="30">
         <v>15</v>
       </c>
@@ -5656,7 +10618,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="30">
         <v>16</v>
       </c>
@@ -5682,7 +10644,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="21" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="30">
         <v>17</v>
       </c>
@@ -5708,7 +10670,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="22" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="30">
         <v>18</v>
       </c>
@@ -5734,7 +10696,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="30">
         <v>19</v>
       </c>
@@ -5760,7 +10722,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="30">
         <v>20</v>
       </c>
@@ -5786,7 +10748,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J25" s="30">
         <v>10</v>
       </c>
@@ -5800,8 +10762,8 @@
         <v>226</v>
       </c>
     </row>
-    <row r="26" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="27" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="34" t="s">
         <v>49</v>
       </c>
@@ -5809,7 +10771,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="13" t="s">
         <v>70</v>
       </c>
@@ -5835,7 +10797,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="30">
         <v>1</v>
       </c>
@@ -5861,7 +10823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="30">
         <v>2</v>
       </c>
@@ -5887,7 +10849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="30">
         <v>3</v>
       </c>
@@ -5913,7 +10875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="30">
         <v>4</v>
       </c>
@@ -5939,7 +10901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="30">
         <v>5</v>
       </c>
@@ -5965,7 +10927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="30">
         <v>6</v>
       </c>
@@ -5991,7 +10953,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B35" s="30">
         <v>7</v>
       </c>
@@ -6017,7 +10979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B36" s="30">
         <v>8</v>
       </c>
@@ -6043,7 +11005,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B37" s="30">
         <v>9</v>
       </c>
@@ -6069,7 +11031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B38" s="30">
         <v>10</v>
       </c>
@@ -6095,7 +11057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B39" s="30">
         <v>11</v>
       </c>
@@ -6121,7 +11083,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B40" s="30">
         <v>12</v>
       </c>
@@ -6147,7 +11109,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B41" s="30">
         <v>13</v>
       </c>
@@ -6173,13 +11135,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="43" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B43" s="34" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B44" s="13" t="s">
         <v>114</v>
       </c>
@@ -6202,7 +11164,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B45" s="30">
         <v>1</v>
       </c>
@@ -6225,7 +11187,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B46" s="30">
         <v>2</v>
       </c>
@@ -6248,7 +11210,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B47" s="30">
         <v>3</v>
       </c>
@@ -6271,7 +11233,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B48" s="30">
         <v>4</v>
       </c>
@@ -6294,7 +11256,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B49" s="30">
         <v>5</v>
       </c>
@@ -6317,7 +11279,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="30">
         <v>6</v>
       </c>
@@ -6340,7 +11302,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="30">
         <v>7</v>
       </c>
@@ -6363,7 +11325,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B52" s="30">
         <v>8</v>
       </c>
@@ -6386,7 +11348,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B53" s="30">
         <v>9</v>
       </c>
@@ -6409,7 +11371,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B54" s="30">
         <v>10</v>
       </c>
@@ -6432,13 +11394,13 @@
         <v>197</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="56" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B56" s="34" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B57" s="13" t="s">
         <v>99</v>
       </c>
@@ -6464,7 +11426,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B58" s="30">
         <v>1</v>
       </c>
@@ -6490,7 +11452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B59" s="30">
         <v>2</v>
       </c>
@@ -6516,7 +11478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B60" s="30">
         <v>3</v>
       </c>
@@ -6542,7 +11504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B61" s="30">
         <v>4</v>
       </c>
@@ -6568,7 +11530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B62" s="30">
         <v>5</v>
       </c>
@@ -6594,7 +11556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B63" s="30">
         <v>6</v>
       </c>
@@ -6620,7 +11582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B64" s="30">
         <v>7</v>
       </c>
@@ -6646,7 +11608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B65" s="30">
         <v>8</v>
       </c>
@@ -6672,7 +11634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B66" s="30">
         <v>9</v>
       </c>
@@ -6698,7 +11660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B67" s="30">
         <v>10</v>
       </c>
@@ -6724,14 +11686,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="69" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="70" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B70" s="35" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B71" s="13" t="s">
         <v>109</v>
       </c>
@@ -6748,26 +11710,26 @@
         <v>111</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C73" s="56" t="s">
+    <row r="72" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="73" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C73" s="143" t="s">
         <v>254</v>
       </c>
-      <c r="D73" s="56"/>
-      <c r="E73" s="56"/>
-    </row>
-    <row r="74" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C74" s="56"/>
-      <c r="D74" s="56"/>
-      <c r="E74" s="56"/>
-    </row>
-    <row r="75" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D73" s="143"/>
+      <c r="E73" s="143"/>
+    </row>
+    <row r="74" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C74" s="143"/>
+      <c r="D74" s="143"/>
+      <c r="E74" s="143"/>
+    </row>
+    <row r="75" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="76" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B76" s="35" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B77" s="13" t="s">
         <v>112</v>
       </c>
@@ -6781,25 +11743,25 @@
         <v>113</v>
       </c>
     </row>
-    <row r="78" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C79" s="56" t="s">
+    <row r="78" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="79" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C79" s="143" t="s">
         <v>254</v>
       </c>
-      <c r="D79" s="56"/>
-    </row>
-    <row r="80" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C80" s="56"/>
-      <c r="D80" s="56"/>
-    </row>
-    <row r="81" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D79" s="143"/>
+    </row>
+    <row r="80" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C80" s="143"/>
+      <c r="D80" s="143"/>
+    </row>
+    <row r="81" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="82" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="83" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B83" s="34" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B84" s="13" t="s">
         <v>83</v>
       </c>
@@ -6819,44 +11781,44 @@
         <v>63</v>
       </c>
     </row>
-    <row r="85" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B85" s="29" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="86" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C86" s="57" t="s">
+    <row r="86" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C86" s="144" t="s">
         <v>260</v>
       </c>
-      <c r="D86" s="56"/>
-      <c r="E86" s="56"/>
-      <c r="F86" s="56"/>
-    </row>
-    <row r="87" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C87" s="56"/>
-      <c r="D87" s="56"/>
-      <c r="E87" s="56"/>
-      <c r="F87" s="56"/>
-    </row>
-    <row r="88" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C88" s="56"/>
-      <c r="D88" s="56"/>
-      <c r="E88" s="56"/>
-      <c r="F88" s="56"/>
-    </row>
-    <row r="89" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C89" s="56"/>
-      <c r="D89" s="56"/>
-      <c r="E89" s="56"/>
-      <c r="F89" s="56"/>
-    </row>
-    <row r="90" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D86" s="143"/>
+      <c r="E86" s="143"/>
+      <c r="F86" s="143"/>
+    </row>
+    <row r="87" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C87" s="143"/>
+      <c r="D87" s="143"/>
+      <c r="E87" s="143"/>
+      <c r="F87" s="143"/>
+    </row>
+    <row r="88" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C88" s="143"/>
+      <c r="D88" s="143"/>
+      <c r="E88" s="143"/>
+      <c r="F88" s="143"/>
+    </row>
+    <row r="89" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C89" s="143"/>
+      <c r="D89" s="143"/>
+      <c r="E89" s="143"/>
+      <c r="F89" s="143"/>
+    </row>
+    <row r="90" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="91" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B91" s="34" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B92" s="13" t="s">
         <v>65</v>
       </c>
@@ -6864,27 +11826,27 @@
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="58" t="s">
+    <row r="93" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B93" s="145" t="s">
         <v>257</v>
       </c>
-      <c r="C93" s="58"/>
-    </row>
-    <row r="94" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B94" s="56"/>
-      <c r="C94" s="56"/>
-    </row>
-    <row r="95" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="56"/>
-      <c r="C95" s="56"/>
-    </row>
-    <row r="96" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="97" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C93" s="145"/>
+    </row>
+    <row r="94" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B94" s="143"/>
+      <c r="C94" s="143"/>
+    </row>
+    <row r="95" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B95" s="143"/>
+      <c r="C95" s="143"/>
+    </row>
+    <row r="96" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="97" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B97" s="34" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="98" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B98" s="13" t="s">
         <v>81</v>
       </c>
@@ -6898,12 +11860,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="99" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="59" t="s">
+    <row r="99" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B99" s="142" t="s">
         <v>258</v>
       </c>
-      <c r="C99" s="59"/>
-      <c r="D99" s="59"/>
+      <c r="C99" s="142"/>
+      <c r="D99" s="142"/>
       <c r="F99" s="13" t="s">
         <v>88</v>
       </c>
@@ -6917,15 +11879,15 @@
         <v>124</v>
       </c>
     </row>
-    <row r="100" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="59"/>
-      <c r="C100" s="59"/>
-      <c r="D100" s="59"/>
-    </row>
-    <row r="101" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="59"/>
-      <c r="C101" s="59"/>
-      <c r="D101" s="59"/>
+    <row r="100" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B100" s="142"/>
+      <c r="C100" s="142"/>
+      <c r="D100" s="142"/>
+    </row>
+    <row r="101" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B101" s="142"/>
+      <c r="C101" s="142"/>
+      <c r="D101" s="142"/>
       <c r="F101" s="33" t="s">
         <v>274</v>
       </c>
@@ -6936,7 +11898,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="102" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B102" s="29">
         <v>1</v>
       </c>
@@ -6956,7 +11918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B103" s="29">
         <v>1</v>
       </c>
@@ -6976,7 +11938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B104" s="29">
         <v>2</v>
       </c>
@@ -6996,7 +11958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B105" s="29">
         <v>2</v>
       </c>
@@ -7013,7 +11975,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="106" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B106" s="29">
         <v>3</v>
       </c>
@@ -7024,7 +11986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B107" s="29">
         <v>3</v>
       </c>
@@ -7035,7 +11997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B108" s="29">
         <v>4</v>
       </c>
@@ -7046,7 +12008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B109" s="29">
         <v>4</v>
       </c>
@@ -7057,7 +12019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B110" s="29">
         <v>5</v>
       </c>
@@ -7068,7 +12030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B111" s="29">
         <v>5</v>
       </c>
@@ -7079,7 +12041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B112" s="29">
         <v>5</v>
       </c>
@@ -7090,7 +12052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B113" s="29">
         <v>5</v>
       </c>
@@ -7101,7 +12063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B114" s="29">
         <v>6</v>
       </c>
@@ -7112,7 +12074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B115" s="29">
         <v>7</v>
       </c>
@@ -7123,7 +12085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B116" s="29">
         <v>8</v>
       </c>
@@ -7134,7 +12096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B117" s="29">
         <v>8</v>
       </c>
@@ -7145,7 +12107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B118" s="29">
         <v>8</v>
       </c>
@@ -7156,7 +12118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B119" s="29">
         <v>9</v>
       </c>
@@ -7167,7 +12129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B120" s="29">
         <v>9</v>
       </c>
@@ -7178,7 +12140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B121" s="29">
         <v>9</v>
       </c>
@@ -7189,7 +12151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B122" s="29">
         <v>9</v>
       </c>
@@ -7200,7 +12162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B123" s="29">
         <v>9</v>
       </c>
@@ -7211,7 +12173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B124" s="29">
         <v>10</v>
       </c>
@@ -7222,7 +12184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B125" s="29">
         <v>10</v>
       </c>
@@ -7233,7 +12195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B126" s="29">
         <v>11</v>
       </c>
@@ -7244,7 +12206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B127" s="29">
         <v>11</v>
       </c>
@@ -7255,7 +12217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B128" s="29">
         <v>11</v>
       </c>
@@ -7266,7 +12228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B129" s="29">
         <v>11</v>
       </c>
@@ -7277,7 +12239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B130" s="29">
         <v>11</v>
       </c>
@@ -7288,7 +12250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B131" s="29">
         <v>11</v>
       </c>
@@ -7299,7 +12261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B132" s="29">
         <v>12</v>
       </c>
@@ -7310,7 +12272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B133" s="29">
         <v>13</v>
       </c>
@@ -7321,7 +12283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B134" s="29">
         <v>13</v>
       </c>
@@ -7332,122 +12294,122 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="21.95" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="135" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="136" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="137" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="138" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="139" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="140" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="141" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="142" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="143" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="144" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="145" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="146" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="147" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="148" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="149" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="150" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="151" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="152" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="153" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="154" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="155" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="156" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="157" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="158" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="159" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="160" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="161" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="162" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="163" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="164" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="165" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="166" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="167" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="168" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="169" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="170" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="171" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="172" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="173" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="174" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="175" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="176" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="177" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="178" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="179" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="180" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="181" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="182" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="183" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="184" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="185" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="186" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="187" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="188" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="189" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="190" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="191" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="192" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="193" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="194" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="195" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="196" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="197" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="198" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="199" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="200" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="201" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="202" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="203" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="204" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="205" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="206" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="207" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="208" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="209" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="210" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="211" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="212" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="213" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="214" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="215" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="216" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="217" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="218" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="219" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="220" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="221" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="222" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="223" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="224" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="225" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="226" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="227" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="228" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="229" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="230" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="231" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="232" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="233" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="234" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="235" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="236" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="237" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="238" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="239" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="240" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="241" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="242" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="243" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="244" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="245" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="246" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="247" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="248" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="249" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="250" ht="21.95" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="C73:E74"/>
